--- a/data/kapitola_07.xlsx
+++ b/data/kapitola_07.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB121DE8-2EA7-4B67-9D06-BA695C32893B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA5AAECC-8540-486B-ADF6-E18993572D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{02248589-D1F7-48A7-B4D4-AF9361169766}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{7F358E05-1A53-46D8-959C-57B782BAF302}"/>
   </bookViews>
   <sheets>
     <sheet name="Prehled" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="180">
   <si>
     <t>Interval spolehlivosti při známé σ</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Pro 0,95 je úroveň kvantilu 0,975.</t>
   </si>
   <si>
-    <t>Interval zachytí μ v 95 % opakování postupu;</t>
-  </si>
-  <si>
     <t>jeden interval μ buď obsahuje, nebo ne.</t>
   </si>
   <si>
@@ -177,24 +174,12 @@
     <t>Horní hranice ekvivalence</t>
   </si>
   <si>
-    <t>Test rozdílu: dolní mez 95% intervalu</t>
-  </si>
-  <si>
-    <t>Test rozdílu: horní mez 95% intervalu</t>
-  </si>
-  <si>
     <t>Test rozdílu: oboustranná p-hodnota</t>
   </si>
   <si>
     <t>Test rozdílu: rozhodnutí</t>
   </si>
   <si>
-    <t>Test ekvivalence: dolní mez 90% intervalu</t>
-  </si>
-  <si>
-    <t>Test ekvivalence: horní mez 90% intervalu</t>
-  </si>
-  <si>
     <t>Test ekvivalence: závěr</t>
   </si>
   <si>
@@ -219,19 +204,13 @@
     <t>Hranice stanovte před analýzou, ne podle výsledku.</t>
   </si>
   <si>
-    <t>95% interval slouží testu rozdílu od normy.</t>
-  </si>
-  <si>
-    <t>90% interval slouží testu ekvivalence:</t>
-  </si>
-  <si>
     <t>dva jednostranné testy, každý na hladině B7.</t>
   </si>
   <si>
-    <t>Ekvivalence jen tehdy, leží-li celý 90% interval v pásmu.</t>
-  </si>
-  <si>
-    <t>Větší z obou p-hodnot; menší než B7 znamená ekvivalenci.</t>
+    <t>Interval nesmí přesáhnout hranice; přesný dotyk připouštíme.</t>
+  </si>
+  <si>
+    <t>Větší z obou p-hodnot; nejvýše B7 znamená ekvivalenci.</t>
   </si>
   <si>
     <t>Vstup</t>
@@ -701,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -731,13 +710,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1099,7 +1084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D29A4B-C158-4F52-8698-0602A4D4B2C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7F8500-873D-4111-A43D-A7560B988938}">
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1108,11 +1093,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="A1" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="2" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1120,240 +1105,240 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
+      <c r="A3" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
+      <c r="A4" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
     </row>
     <row r="5" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
     </row>
     <row r="7" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1384,7 +1369,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA6E0AC-2174-49EB-B9ED-6CB6A6401450}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E78151DA-05CF-4295-836B-8472D8744DD9}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1395,54 +1380,54 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>66</v>
+      <c r="D1" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="15">
         <v>15</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>94</v>
+      <c r="D2" s="18" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="15">
         <v>36</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="15">
         <v>104.5</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>95</v>
+      <c r="D4" s="18" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D5" s="15"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="15"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1454,7 +1439,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA545AC-C514-4670-8DE5-1087726B2633}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43D5EA3-54C0-4616-8A33-217BE3986ADF}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1465,54 +1450,54 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>66</v>
+      <c r="D1" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="15">
         <v>10</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>99</v>
+      <c r="D2" s="18" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="15">
         <v>25</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="15">
         <v>100</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>100</v>
+      <c r="D4" s="18" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D5" s="15"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="15"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1524,7 +1509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD73700-9191-4E5A-99F4-CA1A4472523C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E4DCC78-F99F-4F08-8FDC-6C50E0DF4EC6}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1534,69 +1519,69 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>66</v>
+        <v>94</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="15">
         <v>12</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>102</v>
+      <c r="C2" s="18" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+      <c r="A3" s="15">
         <v>15</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="17"/>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="15">
         <v>9</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>103</v>
+      <c r="C4" s="18" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="15">
         <v>14</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="17"/>
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="15">
         <v>11</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
+      <c r="A7" s="15">
         <v>13</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="17"/>
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="15">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+      <c r="A9" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+      <c r="A10" s="15">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="A11" s="15">
         <v>14</v>
       </c>
     </row>
@@ -1610,7 +1595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C62B9F6-F97B-429D-B6BE-BE188C4977E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA25C09A-9B5A-4908-9694-E728E0F2AA74}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1621,60 +1606,60 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>66</v>
+      <c r="D1" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="15">
         <v>30</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>105</v>
+      <c r="D2" s="18" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="15">
         <v>16</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="15">
         <v>32.4</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>100</v>
+      <c r="D4" s="18" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="15">
         <v>4.8</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="15"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1686,7 +1671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DDBF6B-7BD6-4A20-BCF5-39B4F85B6A0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E74FA6-DB2B-4AB1-AB0B-BF58C5283F79}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1696,119 +1681,119 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>66</v>
+        <v>99</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="15">
         <v>18</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>107</v>
+      <c r="C2" s="18" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+      <c r="A3" s="15">
         <v>22</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="17"/>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="15">
         <v>25</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>108</v>
+      <c r="C4" s="18" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="15">
         <v>19</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="17"/>
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="15">
         <v>24</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
+      <c r="A7" s="15">
         <v>21</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="17"/>
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="15">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+      <c r="A9" s="15">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+      <c r="A10" s="15">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="A11" s="15">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
+      <c r="A12" s="15">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
+      <c r="A13" s="15">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+      <c r="A14" s="15">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
+      <c r="A15" s="15">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
+      <c r="A16" s="15">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
+      <c r="A17" s="15">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
+      <c r="A18" s="15">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13">
+      <c r="A19" s="15">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+      <c r="A20" s="15">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13">
+      <c r="A21" s="15">
         <v>22</v>
       </c>
     </row>
@@ -1822,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E4CF77-EE94-4006-8D36-0FDE47643C73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A66FFD-F61E-458C-9D41-B6108700D87E}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1832,102 +1817,102 @@
   <sheetData>
     <row r="1" spans="1:6" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="15">
+        <v>480</v>
+      </c>
+      <c r="D2" s="15">
+        <v>495</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="15">
+        <v>490</v>
+      </c>
+      <c r="D3" s="15">
+        <v>515</v>
+      </c>
+      <c r="F3" s="17"/>
+    </row>
+    <row r="4" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="15">
+        <v>500</v>
+      </c>
+      <c r="D4" s="15">
+        <v>520</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="B5" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="15">
+        <v>505</v>
+      </c>
+      <c r="D5" s="15">
+        <v>540</v>
+      </c>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="B6" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="13">
-        <v>480</v>
-      </c>
-      <c r="D2" s="13">
-        <v>495</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="13">
-        <v>490</v>
-      </c>
-      <c r="D3" s="13">
-        <v>515</v>
-      </c>
-      <c r="F3" s="15"/>
-    </row>
-    <row r="4" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="13">
-        <v>500</v>
-      </c>
-      <c r="D4" s="13">
-        <v>520</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="13">
-        <v>505</v>
-      </c>
-      <c r="D5" s="13">
-        <v>540</v>
-      </c>
-      <c r="F5" s="15"/>
-    </row>
-    <row r="6" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="13">
+      <c r="C6" s="15">
         <v>492</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="15">
         <v>498</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F7" s="15"/>
+      <c r="F7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1939,7 +1924,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB93EF8-4A5D-4339-BC81-73ADA3A5A143}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5802A304-B50D-4D72-9DE7-6A12956BA0F2}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1950,60 +1935,60 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>66</v>
+      <c r="D1" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="15">
         <v>15</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>125</v>
+      <c r="D2" s="18" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="15">
         <v>6</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="15">
         <v>25</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>126</v>
+      <c r="D4" s="18" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="15">
         <v>2</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="15"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2015,7 +2000,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AEF721-FF8D-41F7-8271-36AD545A3AC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB4CDC6-614A-49C1-919D-45FB35EE737C}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2026,66 +2011,66 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>66</v>
+      <c r="D1" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="15">
+        <v>25</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="13">
-        <v>25</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>128</v>
-      </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="15">
         <v>2</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="15">
         <v>25.6</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>129</v>
+      <c r="D4" s="18" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="15">
         <v>6</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="A6" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="15">
         <v>150</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2097,7 +2082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E4D8D9-9446-4CFF-9710-EB49EEDBC483}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF74184-A6B4-41A5-A9FB-B6D772D306B0}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2107,120 +2092,120 @@
   <sheetData>
     <row r="1" spans="1:7" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="15">
+        <v>473.6</v>
+      </c>
+      <c r="C2" s="15">
+        <v>511.4</v>
+      </c>
+      <c r="D2" s="15">
+        <v>476.6</v>
+      </c>
+      <c r="E2" s="15">
+        <v>508.4</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="15">
+        <v>503</v>
+      </c>
+      <c r="C3" s="15">
+        <v>512</v>
+      </c>
+      <c r="D3" s="15">
+        <v>503.7</v>
+      </c>
+      <c r="E3" s="15">
+        <v>511.3</v>
+      </c>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="15">
+        <v>488</v>
+      </c>
+      <c r="C4" s="15">
+        <v>506</v>
+      </c>
+      <c r="D4" s="15">
+        <v>489.4</v>
+      </c>
+      <c r="E4" s="15">
+        <v>504.6</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="B5" s="15">
+        <v>525</v>
+      </c>
+      <c r="C5" s="15">
+        <v>560</v>
+      </c>
+      <c r="D5" s="15">
+        <v>527.79999999999995</v>
+      </c>
+      <c r="E5" s="15">
+        <v>557.20000000000005</v>
+      </c>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="13">
-        <v>473.6</v>
-      </c>
-      <c r="C2" s="13">
-        <v>511.4</v>
-      </c>
-      <c r="D2" s="13">
-        <v>476.6</v>
-      </c>
-      <c r="E2" s="13">
-        <v>508.4</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="13">
-        <v>503</v>
-      </c>
-      <c r="C3" s="13">
-        <v>512</v>
-      </c>
-      <c r="D3" s="13">
-        <v>503.7</v>
-      </c>
-      <c r="E3" s="13">
-        <v>511.3</v>
-      </c>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="13">
-        <v>488</v>
-      </c>
-      <c r="C4" s="13">
-        <v>506</v>
-      </c>
-      <c r="D4" s="13">
-        <v>489.4</v>
-      </c>
-      <c r="E4" s="13">
-        <v>504.6</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="13">
-        <v>525</v>
-      </c>
-      <c r="C5" s="13">
-        <v>560</v>
-      </c>
-      <c r="D5" s="13">
-        <v>527.79999999999995</v>
-      </c>
-      <c r="E5" s="13">
-        <v>557.20000000000005</v>
-      </c>
-      <c r="G5" s="15"/>
-    </row>
-    <row r="6" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="B6" s="15">
         <v>505</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="15">
         <v>535</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="15">
         <v>507.4</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="15">
         <v>532.6</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G7" s="15"/>
+      <c r="G7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2232,7 +2217,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5B7D66-FD8A-498A-8211-58001842EDE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDCDED2D-5F16-43DF-B620-CFEE5252AB68}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2243,66 +2228,66 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>66</v>
+      <c r="D1" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="15">
         <v>50</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>142</v>
+      <c r="D2" s="18" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="15">
         <v>3</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="15">
         <v>48.2</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>143</v>
+      <c r="D4" s="18" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="15">
         <v>10</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="A6" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="15">
         <v>200</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2314,7 +2299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A6D066-A6C9-491E-AFB1-2BFFBBE9F604}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3702512B-573B-42EF-8BA6-2A9B53B380D5}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2336,7 +2321,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2350,8 +2335,8 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="5">
@@ -2376,7 +2361,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -2411,7 +2396,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2439,7 +2424,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2448,13 +2433,14 @@
         <v>42.080072030919894</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="10" t="s">
-        <v>15</v>
+      <c r="D10" s="11" t="str">
+        <f>"Interval zachytí μ v "&amp;(100*B5)&amp;" % opakování postupu;"</f>
+        <v>Interval zachytí μ v 95 % opakování postupu;</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2464,7 +2450,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2595,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF78AF2-67FB-426A-A4FE-EDEBBEDB623A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4CC5FC-7F36-444F-A54A-8D2E46AD4BE4}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2607,7 +2593,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -2617,7 +2603,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2631,16 +2617,16 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5">
         <v>10</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2657,7 +2643,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -2681,7 +2667,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="7">
         <f>B3/SQRT(B4)</f>
@@ -2694,9 +2680,9 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="11">
+        <v>19</v>
+      </c>
+      <c r="B8" s="12">
         <f>B4-1</f>
         <v>24</v>
       </c>
@@ -2705,9 +2691,9 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="8">
         <f>_xlfn.T.INV(1-(1-B5)/2,B8)</f>
@@ -2715,7 +2701,7 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2746,7 +2732,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -2756,7 +2742,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2879,7 +2865,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE59F264-1A85-4F94-A002-8609DF37571E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4D95A8-2A06-412C-AF7D-139627EF1BDC}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2891,7 +2877,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -2901,9 +2887,9 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="5">
         <v>50</v>
@@ -2929,7 +2915,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="5">
         <v>10</v>
@@ -2951,9 +2937,9 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="5">
         <v>0.05</v>
@@ -2975,7 +2961,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="7">
         <f>B4/SQRT(B5)</f>
@@ -2988,9 +2974,9 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="11">
+        <v>19</v>
+      </c>
+      <c r="B9" s="12">
         <f>B5-1</f>
         <v>24</v>
       </c>
@@ -3001,7 +2987,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="7">
         <f>(B3-B2)/B8</f>
@@ -3012,9 +2998,9 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="8">
         <f>_xlfn.T.DIST(B10,B9,TRUE)</f>
@@ -3022,14 +3008,14 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="8">
         <f>1-_xlfn.T.DIST(B10,B9,TRUE)</f>
@@ -3040,9 +3026,9 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="8">
         <f>_xlfn.T.DIST.2T(ABS(B10),B9)</f>
@@ -3050,14 +3036,14 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="8">
         <f>_xlfn.T.INV.2T(B6,B9)</f>
@@ -3065,7 +3051,7 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -3172,7 +3158,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18051AE6-2D51-4424-A332-1E1601357557}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFABC76-7C1A-49FD-A164-638E6BD096D3}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3184,7 +3170,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -3194,30 +3180,30 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="5">
         <v>50</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="5">
         <v>3</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -3236,7 +3222,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5">
         <v>10</v>
@@ -3258,9 +3244,9 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5">
         <v>0.05</v>
@@ -3282,7 +3268,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7">
         <f>B5/SQRT(B6)</f>
@@ -3295,9 +3281,9 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="11">
+        <v>19</v>
+      </c>
+      <c r="B10" s="12">
         <f>B6-1</f>
         <v>399</v>
       </c>
@@ -3308,7 +3294,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="9">
         <f>B2-B3</f>
@@ -3321,7 +3307,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="9">
         <f>B2+B3</f>
@@ -3340,24 +3326,27 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>41</v>
+    <row r="14" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="str">
+        <f>"Test rozdílu: dolní mez "&amp;(100*(1-B7))&amp;"% intervalu"</f>
+        <v>Test rozdílu: dolní mez 95% intervalu</v>
       </c>
       <c r="B14" s="9">
         <f>B4-_xlfn.T.INV(1-B7/2,B10)*B9</f>
         <v>47.517036352039554</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="10" t="s">
-        <v>55</v>
+      <c r="D14" s="11" t="str">
+        <f>(100*(1-B7))&amp;"% interval slouží testu rozdílu od normy."</f>
+        <v>95% interval slouží testu rozdílu od normy.</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>42</v>
+      <c r="A15" s="1" t="str">
+        <f>"Test rozdílu: horní mez "&amp;(100*(1-B7))&amp;"% intervalu"</f>
+        <v>Test rozdílu: horní mez 95% intervalu</v>
       </c>
       <c r="B15" s="9">
         <f>B4+_xlfn.T.INV(1-B7/2,B10)*B9</f>
@@ -3370,7 +3359,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B16" s="8">
         <f>_xlfn.T.DIST.2T(ABS((B4-B2)/B9),B10)</f>
@@ -3383,9 +3372,9 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="12" t="str">
+        <v>41</v>
+      </c>
+      <c r="B17" s="13" t="str">
         <f>IF(B16&lt;=B7,"zamítáme nulovou hypotézu","nulovou hypotézu nezamítáme")</f>
         <v>zamítáme nulovou hypotézu</v>
       </c>
@@ -3394,24 +3383,27 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>45</v>
+    <row r="18" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="str">
+        <f>"Test ekvivalence: dolní mez "&amp;(100*(1-2*B7))&amp;"% intervalu"</f>
+        <v>Test ekvivalence: dolní mez 90% intervalu</v>
       </c>
       <c r="B18" s="9">
         <f>B4-_xlfn.T.INV(1-B7,B10)*B9</f>
         <v>47.675659233222284</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="10" t="s">
-        <v>56</v>
+      <c r="D18" s="11" t="str">
+        <f>(100*(1-2*B7))&amp;"% interval slouží testu ekvivalence:"</f>
+        <v>90% interval slouží testu ekvivalence:</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>46</v>
+    <row r="19" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="str">
+        <f>"Test ekvivalence: horní mez "&amp;(100*(1-2*B7))&amp;"% intervalu"</f>
+        <v>Test ekvivalence: horní mez 90% intervalu</v>
       </c>
       <c r="B19" s="9">
         <f>B4+_xlfn.T.INV(1-B7,B10)*B9</f>
@@ -3419,22 +3411,22 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="12" t="str">
-        <f>IF(AND(B18&gt;B11,B19&lt;B12),"ekvivalence doložena","ekvivalence nedoložena")</f>
+        <v>42</v>
+      </c>
+      <c r="B20" s="13" t="str">
+        <f>IF(AND(B18&gt;=B11,B19&lt;=B12),"ekvivalence doložena","ekvivalence nedoložena")</f>
         <v>ekvivalence doložena</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -3449,7 +3441,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B22" s="7">
         <f>(B4-B11)/B9</f>
@@ -3462,7 +3454,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B23" s="8">
         <f>1-_xlfn.T.DIST(B22,B10,TRUE)</f>
@@ -3475,7 +3467,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B24" s="7">
         <f>(B4-B12)/B9</f>
@@ -3488,7 +3480,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B25" s="8">
         <f>_xlfn.T.DIST(B24,B10,TRUE)</f>
@@ -3499,9 +3491,9 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B26" s="8">
         <f>MAX(B23,B25)</f>
@@ -3509,7 +3501,7 @@
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="10" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -3520,7 +3512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF052D5-1606-4B91-B60B-D8F35EB6E9CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D47865-12D1-4EAF-B618-D59A150A4484}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3531,78 +3523,78 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="15">
+        <v>50</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="15">
+        <v>10</v>
+      </c>
+      <c r="D3" s="17"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="15">
+        <v>25</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="13">
-        <v>50</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="13">
+    </row>
+    <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="15">
+        <v>46</v>
+      </c>
+      <c r="D5" s="17"/>
+    </row>
+    <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="15">
         <v>10</v>
       </c>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="13">
-        <v>25</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="13">
-        <v>46</v>
-      </c>
-      <c r="D5" s="15"/>
-    </row>
-    <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="13">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="15">
         <v>0.95</v>
       </c>
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
     <row r="8" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="15">
         <v>0.05</v>
       </c>
     </row>
@@ -3616,7 +3608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2580A13-6028-43F1-A4D6-D02C1FA58F4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37BC2E3-EC13-46F7-908D-7403BAB346B8}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3627,60 +3619,60 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="15">
+        <v>100</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="13">
-        <v>100</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="15">
         <v>56</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="15">
         <v>104.125</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>74</v>
+      <c r="D4" s="18" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="15">
         <v>12.584</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="15"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="15"/>
+      <c r="D7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3692,7 +3684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{111A2FD0-A9FD-4A8F-9FE6-B8A115519E37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD6727E8-A514-4123-99C3-0C0C20FF0199}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3702,102 +3694,102 @@
   <sheetData>
     <row r="1" spans="1:6" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="15">
+        <v>46</v>
+      </c>
+      <c r="C2" s="15">
+        <v>10</v>
+      </c>
+      <c r="D2" s="15">
+        <v>25</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="15">
+        <v>48.5</v>
+      </c>
+      <c r="C3" s="15">
+        <v>10</v>
+      </c>
+      <c r="D3" s="15">
+        <v>400</v>
+      </c>
+      <c r="F3" s="17"/>
+    </row>
+    <row r="4" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="15">
+        <v>50.4</v>
+      </c>
+      <c r="C4" s="15">
+        <v>10</v>
+      </c>
+      <c r="D4" s="15">
+        <v>400</v>
+      </c>
+      <c r="F4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="13">
-        <v>46</v>
-      </c>
-      <c r="C2" s="13">
+    </row>
+    <row r="5" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="15">
+        <v>44</v>
+      </c>
+      <c r="C5" s="15">
         <v>10</v>
       </c>
-      <c r="D2" s="13">
-        <v>25</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="13">
-        <v>48.5</v>
-      </c>
-      <c r="C3" s="13">
+      <c r="D5" s="15">
+        <v>100</v>
+      </c>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="15">
+        <v>47</v>
+      </c>
+      <c r="C6" s="15">
         <v>10</v>
       </c>
-      <c r="D3" s="13">
-        <v>400</v>
-      </c>
-      <c r="F3" s="15"/>
-    </row>
-    <row r="4" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="13">
-        <v>50.4</v>
-      </c>
-      <c r="C4" s="13">
-        <v>10</v>
-      </c>
-      <c r="D4" s="13">
-        <v>400</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="13">
-        <v>44</v>
-      </c>
-      <c r="C5" s="13">
-        <v>10</v>
-      </c>
-      <c r="D5" s="13">
+      <c r="D6" s="15">
         <v>100</v>
       </c>
-      <c r="F5" s="15"/>
-    </row>
-    <row r="6" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="13">
-        <v>47</v>
-      </c>
-      <c r="C6" s="13">
-        <v>10</v>
-      </c>
-      <c r="D6" s="13">
-        <v>100</v>
-      </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F7" s="15"/>
+      <c r="F7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3809,7 +3801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A35758-F30E-401D-9314-0B3AC19958E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CAB5280-C020-4E30-8719-1FF1ECD4670C}">
   <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3819,2640 +3811,2640 @@
   <sheetData>
     <row r="1" spans="1:10" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22">
+        <v>48.058999999999997</v>
+      </c>
+      <c r="B2" s="22">
+        <v>10.952</v>
+      </c>
+      <c r="C2" s="22">
+        <v>44.14</v>
+      </c>
+      <c r="D2" s="22">
+        <v>51.978999999999999</v>
+      </c>
+      <c r="E2" s="23">
+        <v>1</v>
+      </c>
+      <c r="F2" s="22">
+        <v>43.539000000000001</v>
+      </c>
+      <c r="G2" s="22">
+        <v>52.58</v>
+      </c>
+      <c r="H2" s="23">
+        <v>1</v>
+      </c>
+      <c r="J2" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22">
+        <v>44.823</v>
+      </c>
+      <c r="B3" s="22">
+        <v>10.125</v>
+      </c>
+      <c r="C3" s="22">
+        <v>40.902999999999999</v>
+      </c>
+      <c r="D3" s="22">
+        <v>48.743000000000002</v>
+      </c>
+      <c r="E3" s="23">
+        <v>1</v>
+      </c>
+      <c r="F3" s="22">
+        <v>40.643000000000001</v>
+      </c>
+      <c r="G3" s="22">
+        <v>49.002000000000002</v>
+      </c>
+      <c r="H3" s="23">
+        <v>1</v>
+      </c>
+      <c r="J3" s="17"/>
+    </row>
+    <row r="4" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22">
+        <v>46.776000000000003</v>
+      </c>
+      <c r="B4" s="22">
+        <v>6.7850000000000001</v>
+      </c>
+      <c r="C4" s="22">
+        <v>42.856000000000002</v>
+      </c>
+      <c r="D4" s="22">
+        <v>50.695999999999998</v>
+      </c>
+      <c r="E4" s="23">
+        <v>1</v>
+      </c>
+      <c r="F4" s="22">
+        <v>43.975000000000001</v>
+      </c>
+      <c r="G4" s="22">
+        <v>49.576999999999998</v>
+      </c>
+      <c r="H4" s="23">
+        <v>1</v>
+      </c>
+      <c r="J4" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
-        <v>48.058999999999997</v>
-      </c>
-      <c r="B2" s="20">
-        <v>10.952</v>
-      </c>
-      <c r="C2" s="20">
-        <v>44.14</v>
-      </c>
-      <c r="D2" s="20">
-        <v>51.978999999999999</v>
-      </c>
-      <c r="E2" s="21">
-        <v>1</v>
-      </c>
-      <c r="F2" s="20">
-        <v>43.539000000000001</v>
-      </c>
-      <c r="G2" s="20">
-        <v>52.58</v>
-      </c>
-      <c r="H2" s="21">
-        <v>1</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
-        <v>44.823</v>
-      </c>
-      <c r="B3" s="20">
-        <v>10.125</v>
-      </c>
-      <c r="C3" s="20">
-        <v>40.902999999999999</v>
-      </c>
-      <c r="D3" s="20">
-        <v>48.743000000000002</v>
-      </c>
-      <c r="E3" s="21">
-        <v>1</v>
-      </c>
-      <c r="F3" s="20">
-        <v>40.643000000000001</v>
-      </c>
-      <c r="G3" s="20">
-        <v>49.002000000000002</v>
-      </c>
-      <c r="H3" s="21">
-        <v>1</v>
-      </c>
-      <c r="J3" s="15"/>
-    </row>
-    <row r="4" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
-        <v>46.776000000000003</v>
-      </c>
-      <c r="B4" s="20">
-        <v>6.7850000000000001</v>
-      </c>
-      <c r="C4" s="20">
-        <v>42.856000000000002</v>
-      </c>
-      <c r="D4" s="20">
-        <v>50.695999999999998</v>
-      </c>
-      <c r="E4" s="21">
-        <v>1</v>
-      </c>
-      <c r="F4" s="20">
-        <v>43.975000000000001</v>
-      </c>
-      <c r="G4" s="20">
-        <v>49.576999999999998</v>
-      </c>
-      <c r="H4" s="21">
-        <v>1</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="5" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+      <c r="A5" s="22">
         <v>44.707999999999998</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="22">
         <v>8.3079999999999998</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="22">
         <v>40.787999999999997</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="22">
         <v>48.628</v>
       </c>
-      <c r="E5" s="21">
-        <v>1</v>
-      </c>
-      <c r="F5" s="20">
+      <c r="E5" s="23">
+        <v>1</v>
+      </c>
+      <c r="F5" s="22">
         <v>41.277999999999999</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="22">
         <v>48.137</v>
       </c>
-      <c r="H5" s="21">
-        <v>1</v>
-      </c>
-      <c r="J5" s="15"/>
+      <c r="H5" s="23">
+        <v>1</v>
+      </c>
+      <c r="J5" s="17"/>
     </row>
     <row r="6" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="22">
         <v>45.088999999999999</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="22">
         <v>8.8420000000000005</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="22">
         <v>41.168999999999997</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="22">
         <v>49.009</v>
       </c>
-      <c r="E6" s="21">
-        <v>1</v>
-      </c>
-      <c r="F6" s="20">
+      <c r="E6" s="23">
+        <v>1</v>
+      </c>
+      <c r="F6" s="22">
         <v>41.439</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="22">
         <v>48.738999999999997</v>
       </c>
-      <c r="H6" s="21">
-        <v>1</v>
-      </c>
-      <c r="J6" s="15"/>
+      <c r="H6" s="23">
+        <v>1</v>
+      </c>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+      <c r="A7" s="22">
         <v>45.948999999999998</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="22">
         <v>7.9770000000000003</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="22">
         <v>42.029000000000003</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <v>49.869</v>
       </c>
-      <c r="E7" s="21">
-        <v>1</v>
-      </c>
-      <c r="F7" s="20">
+      <c r="E7" s="23">
+        <v>1</v>
+      </c>
+      <c r="F7" s="22">
         <v>42.655999999999999</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <v>49.241999999999997</v>
       </c>
-      <c r="H7" s="21">
-        <v>1</v>
-      </c>
-      <c r="J7" s="15"/>
+      <c r="H7" s="23">
+        <v>1</v>
+      </c>
+      <c r="J7" s="17"/>
     </row>
     <row r="8" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
+      <c r="A8" s="22">
         <v>45.710999999999999</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="22">
         <v>9.7110000000000003</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="22">
         <v>41.790999999999997</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="22">
         <v>49.631</v>
       </c>
-      <c r="E8" s="21">
-        <v>1</v>
-      </c>
-      <c r="F8" s="20">
+      <c r="E8" s="23">
+        <v>1</v>
+      </c>
+      <c r="F8" s="22">
         <v>41.701999999999998</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <v>49.719000000000001</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
+      <c r="A9" s="22">
         <v>47.033000000000001</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="22">
         <v>11.488</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="22">
         <v>43.113</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="22">
         <v>50.953000000000003</v>
       </c>
-      <c r="E9" s="21">
-        <v>1</v>
-      </c>
-      <c r="F9" s="20">
+      <c r="E9" s="23">
+        <v>1</v>
+      </c>
+      <c r="F9" s="22">
         <v>42.290999999999997</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <v>51.774999999999999</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+      <c r="A10" s="22">
         <v>43.753</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="22">
         <v>8.61</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="22">
         <v>39.832999999999998</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="22">
         <v>47.673000000000002</v>
       </c>
-      <c r="E10" s="21">
-        <v>1</v>
-      </c>
-      <c r="F10" s="20">
+      <c r="E10" s="23">
+        <v>1</v>
+      </c>
+      <c r="F10" s="22">
         <v>40.198999999999998</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="22">
         <v>47.307000000000002</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20">
+      <c r="A11" s="22">
         <v>50.189</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="22">
         <v>9.3789999999999996</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="22">
         <v>46.27</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="22">
         <v>54.109000000000002</v>
       </c>
-      <c r="E11" s="21">
-        <v>1</v>
-      </c>
-      <c r="F11" s="20">
+      <c r="E11" s="23">
+        <v>1</v>
+      </c>
+      <c r="F11" s="22">
         <v>46.317999999999998</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="22">
         <v>54.061</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
+      <c r="A12" s="22">
         <v>49.22</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="22">
         <v>8.2650000000000006</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="22">
         <v>45.3</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="22">
         <v>53.14</v>
       </c>
-      <c r="E12" s="21">
-        <v>1</v>
-      </c>
-      <c r="F12" s="20">
+      <c r="E12" s="23">
+        <v>1</v>
+      </c>
+      <c r="F12" s="22">
         <v>45.808</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="22">
         <v>52.631</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
+      <c r="A13" s="22">
         <v>49.326999999999998</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="22">
         <v>9.4359999999999999</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="22">
         <v>45.406999999999996</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="22">
         <v>53.247</v>
       </c>
-      <c r="E13" s="21">
-        <v>1</v>
-      </c>
-      <c r="F13" s="20">
+      <c r="E13" s="23">
+        <v>1</v>
+      </c>
+      <c r="F13" s="22">
         <v>45.432000000000002</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="22">
         <v>53.222000000000001</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="A14" s="22">
         <v>44.134</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="22">
         <v>7.6269999999999998</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="22">
         <v>40.213999999999999</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="22">
         <v>48.054000000000002</v>
       </c>
-      <c r="E14" s="21">
-        <v>1</v>
-      </c>
-      <c r="F14" s="20">
+      <c r="E14" s="23">
+        <v>1</v>
+      </c>
+      <c r="F14" s="22">
         <v>40.985999999999997</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="22">
         <v>47.281999999999996</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
+      <c r="A15" s="22">
         <v>46.744</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="22">
         <v>10.616</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="22">
         <v>42.823999999999998</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="22">
         <v>50.664000000000001</v>
       </c>
-      <c r="E15" s="21">
-        <v>1</v>
-      </c>
-      <c r="F15" s="20">
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
+      <c r="F15" s="22">
         <v>42.360999999999997</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="22">
         <v>51.125999999999998</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+      <c r="A16" s="22">
         <v>43.478999999999999</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="22">
         <v>9.6159999999999997</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="22">
         <v>39.558999999999997</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="22">
         <v>47.399000000000001</v>
       </c>
-      <c r="E16" s="21">
-        <v>1</v>
-      </c>
-      <c r="F16" s="20">
+      <c r="E16" s="23">
+        <v>1</v>
+      </c>
+      <c r="F16" s="22">
         <v>39.509</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="22">
         <v>47.448</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+      <c r="A17" s="22">
         <v>45.753999999999998</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="22">
         <v>11.154999999999999</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="22">
         <v>41.834000000000003</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="22">
         <v>49.673999999999999</v>
       </c>
-      <c r="E17" s="21">
-        <v>1</v>
-      </c>
-      <c r="F17" s="20">
+      <c r="E17" s="23">
+        <v>1</v>
+      </c>
+      <c r="F17" s="22">
         <v>41.149000000000001</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="22">
         <v>50.357999999999997</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+      <c r="A18" s="22">
         <v>45.808999999999997</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="22">
         <v>9.8130000000000006</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="22">
         <v>41.889000000000003</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="22">
         <v>49.728999999999999</v>
       </c>
-      <c r="E18" s="21">
-        <v>1</v>
-      </c>
-      <c r="F18" s="20">
+      <c r="E18" s="23">
+        <v>1</v>
+      </c>
+      <c r="F18" s="22">
         <v>41.758000000000003</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="22">
         <v>49.859000000000002</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20">
+      <c r="A19" s="22">
         <v>49.216999999999999</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="22">
         <v>10.031000000000001</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="22">
         <v>45.296999999999997</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="22">
         <v>53.137</v>
       </c>
-      <c r="E19" s="21">
-        <v>1</v>
-      </c>
-      <c r="F19" s="20">
+      <c r="E19" s="23">
+        <v>1</v>
+      </c>
+      <c r="F19" s="22">
         <v>45.076000000000001</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="22">
         <v>53.356999999999999</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
+      <c r="A20" s="22">
         <v>46.570999999999998</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="22">
         <v>9.8109999999999999</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="22">
         <v>42.651000000000003</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="22">
         <v>50.491</v>
       </c>
-      <c r="E20" s="21">
-        <v>1</v>
-      </c>
-      <c r="F20" s="20">
+      <c r="E20" s="23">
+        <v>1</v>
+      </c>
+      <c r="F20" s="22">
         <v>42.521999999999998</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="22">
         <v>50.621000000000002</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
+      <c r="A21" s="22">
         <v>42.893999999999998</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="22">
         <v>11.667</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="22">
         <v>38.973999999999997</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="22">
         <v>46.814</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="23">
         <v>0</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="22">
         <v>38.079000000000001</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="22">
         <v>47.71</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20">
+      <c r="A22" s="22">
         <v>51.426000000000002</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="22">
         <v>10.516</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="22">
         <v>47.506</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="22">
         <v>55.345999999999997</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="23">
         <v>0</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="22">
         <v>47.085000000000001</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="22">
         <v>55.765999999999998</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20">
+      <c r="A23" s="22">
         <v>42.328000000000003</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="22">
         <v>12.051</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="22">
         <v>38.408000000000001</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="22">
         <v>46.247999999999998</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="23">
         <v>0</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="22">
         <v>37.353999999999999</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="22">
         <v>47.302999999999997</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20">
+      <c r="A24" s="22">
         <v>48.484000000000002</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="22">
         <v>13.532</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="22">
         <v>44.564</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="22">
         <v>52.404000000000003</v>
       </c>
-      <c r="E24" s="21">
-        <v>1</v>
-      </c>
-      <c r="F24" s="20">
+      <c r="E24" s="23">
+        <v>1</v>
+      </c>
+      <c r="F24" s="22">
         <v>42.898000000000003</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="22">
         <v>54.07</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="20">
+      <c r="A25" s="22">
         <v>49.048999999999999</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="22">
         <v>10.119</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="22">
         <v>45.128999999999998</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="22">
         <v>52.969000000000001</v>
       </c>
-      <c r="E25" s="21">
-        <v>1</v>
-      </c>
-      <c r="F25" s="20">
+      <c r="E25" s="23">
+        <v>1</v>
+      </c>
+      <c r="F25" s="22">
         <v>44.872</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="22">
         <v>53.225999999999999</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20">
+      <c r="A26" s="22">
         <v>46.911000000000001</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="22">
         <v>12.042</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="22">
         <v>42.991</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="22">
         <v>50.831000000000003</v>
       </c>
-      <c r="E26" s="21">
-        <v>1</v>
-      </c>
-      <c r="F26" s="20">
+      <c r="E26" s="23">
+        <v>1</v>
+      </c>
+      <c r="F26" s="22">
         <v>41.941000000000003</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="22">
         <v>51.881999999999998</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20">
+      <c r="A27" s="22">
         <v>46.603000000000002</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="22">
         <v>10.358000000000001</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="22">
         <v>42.683</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="22">
         <v>50.523000000000003</v>
       </c>
-      <c r="E27" s="21">
-        <v>1</v>
-      </c>
-      <c r="F27" s="20">
+      <c r="E27" s="23">
+        <v>1</v>
+      </c>
+      <c r="F27" s="22">
         <v>42.328000000000003</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="22">
         <v>50.878999999999998</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20">
+      <c r="A28" s="22">
         <v>49.093000000000004</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="22">
         <v>7.35</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="22">
         <v>45.173000000000002</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="22">
         <v>53.012999999999998</v>
       </c>
-      <c r="E28" s="21">
-        <v>1</v>
-      </c>
-      <c r="F28" s="20">
+      <c r="E28" s="23">
+        <v>1</v>
+      </c>
+      <c r="F28" s="22">
         <v>46.058999999999997</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="22">
         <v>52.127000000000002</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20">
+      <c r="A29" s="22">
         <v>46.316000000000003</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="22">
         <v>10.512</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="22">
         <v>42.396000000000001</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="22">
         <v>50.234999999999999</v>
       </c>
-      <c r="E29" s="21">
-        <v>1</v>
-      </c>
-      <c r="F29" s="20">
+      <c r="E29" s="23">
+        <v>1</v>
+      </c>
+      <c r="F29" s="22">
         <v>41.976999999999997</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="22">
         <v>50.655000000000001</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20">
+      <c r="A30" s="22">
         <v>47.067</v>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="22">
         <v>14.547000000000001</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="22">
         <v>43.148000000000003</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="22">
         <v>50.987000000000002</v>
       </c>
-      <c r="E30" s="21">
-        <v>1</v>
-      </c>
-      <c r="F30" s="20">
+      <c r="E30" s="23">
+        <v>1</v>
+      </c>
+      <c r="F30" s="22">
         <v>41.063000000000002</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="22">
         <v>53.072000000000003</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H30" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20">
+      <c r="A31" s="22">
         <v>44.073</v>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="22">
         <v>8.6869999999999994</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="22">
         <v>40.152999999999999</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="22">
         <v>47.991999999999997</v>
       </c>
-      <c r="E31" s="21">
-        <v>1</v>
-      </c>
-      <c r="F31" s="20">
+      <c r="E31" s="23">
+        <v>1</v>
+      </c>
+      <c r="F31" s="22">
         <v>40.485999999999997</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="22">
         <v>47.658999999999999</v>
       </c>
-      <c r="H31" s="21">
+      <c r="H31" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20">
+      <c r="A32" s="22">
         <v>46.811999999999998</v>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="22">
         <v>7.5810000000000004</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="22">
         <v>42.892000000000003</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="22">
         <v>50.731999999999999</v>
       </c>
-      <c r="E32" s="21">
-        <v>1</v>
-      </c>
-      <c r="F32" s="20">
+      <c r="E32" s="23">
+        <v>1</v>
+      </c>
+      <c r="F32" s="22">
         <v>43.683</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="22">
         <v>49.942</v>
       </c>
-      <c r="H32" s="21">
+      <c r="H32" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20">
+      <c r="A33" s="22">
         <v>46.722999999999999</v>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="22">
         <v>9.3010000000000002</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="22">
         <v>42.802999999999997</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="22">
         <v>50.643000000000001</v>
       </c>
-      <c r="E33" s="21">
-        <v>1</v>
-      </c>
-      <c r="F33" s="20">
+      <c r="E33" s="23">
+        <v>1</v>
+      </c>
+      <c r="F33" s="22">
         <v>42.883000000000003</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="22">
         <v>50.561999999999998</v>
       </c>
-      <c r="H33" s="21">
+      <c r="H33" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
+      <c r="A34" s="22">
         <v>47.588999999999999</v>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="22">
         <v>10.27</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="22">
         <v>43.67</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="22">
         <v>51.509</v>
       </c>
-      <c r="E34" s="21">
-        <v>1</v>
-      </c>
-      <c r="F34" s="20">
+      <c r="E34" s="23">
+        <v>1</v>
+      </c>
+      <c r="F34" s="22">
         <v>43.35</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="22">
         <v>51.829000000000001</v>
       </c>
-      <c r="H34" s="21">
+      <c r="H34" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20">
+      <c r="A35" s="22">
         <v>47.636000000000003</v>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="22">
         <v>9.1300000000000008</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="22">
         <v>43.716000000000001</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="22">
         <v>51.555</v>
       </c>
-      <c r="E35" s="21">
-        <v>1</v>
-      </c>
-      <c r="F35" s="20">
+      <c r="E35" s="23">
+        <v>1</v>
+      </c>
+      <c r="F35" s="22">
         <v>43.866999999999997</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="22">
         <v>51.404000000000003</v>
       </c>
-      <c r="H35" s="21">
+      <c r="H35" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20">
+      <c r="A36" s="22">
         <v>48.197000000000003</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="22">
         <v>8.0890000000000004</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="22">
         <v>44.277000000000001</v>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="22">
         <v>52.116999999999997</v>
       </c>
-      <c r="E36" s="21">
-        <v>1</v>
-      </c>
-      <c r="F36" s="20">
+      <c r="E36" s="23">
+        <v>1</v>
+      </c>
+      <c r="F36" s="22">
         <v>44.857999999999997</v>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="22">
         <v>51.536000000000001</v>
       </c>
-      <c r="H36" s="21">
+      <c r="H36" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20">
+      <c r="A37" s="22">
         <v>48.54</v>
       </c>
-      <c r="B37" s="20">
+      <c r="B37" s="22">
         <v>8.077</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="22">
         <v>44.62</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="22">
         <v>52.46</v>
       </c>
-      <c r="E37" s="21">
-        <v>1</v>
-      </c>
-      <c r="F37" s="20">
+      <c r="E37" s="23">
+        <v>1</v>
+      </c>
+      <c r="F37" s="22">
         <v>45.206000000000003</v>
       </c>
-      <c r="G37" s="20">
+      <c r="G37" s="22">
         <v>51.874000000000002</v>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="20">
+      <c r="A38" s="22">
         <v>46.853999999999999</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="22">
         <v>7.6710000000000003</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="22">
         <v>42.933999999999997</v>
       </c>
-      <c r="D38" s="20">
+      <c r="D38" s="22">
         <v>50.774000000000001</v>
       </c>
-      <c r="E38" s="21">
-        <v>1</v>
-      </c>
-      <c r="F38" s="20">
+      <c r="E38" s="23">
+        <v>1</v>
+      </c>
+      <c r="F38" s="22">
         <v>43.688000000000002</v>
       </c>
-      <c r="G38" s="20">
+      <c r="G38" s="22">
         <v>50.021000000000001</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20">
+      <c r="A39" s="22">
         <v>44.548999999999999</v>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="22">
         <v>8.8940000000000001</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="22">
         <v>40.628999999999998</v>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="22">
         <v>48.469000000000001</v>
       </c>
-      <c r="E39" s="21">
-        <v>1</v>
-      </c>
-      <c r="F39" s="20">
+      <c r="E39" s="23">
+        <v>1</v>
+      </c>
+      <c r="F39" s="22">
         <v>40.878</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="22">
         <v>48.220999999999997</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="20">
+      <c r="A40" s="22">
         <v>46.652999999999999</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="22">
         <v>9.5570000000000004</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="22">
         <v>42.734000000000002</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="22">
         <v>50.573</v>
       </c>
-      <c r="E40" s="21">
-        <v>1</v>
-      </c>
-      <c r="F40" s="20">
+      <c r="E40" s="23">
+        <v>1</v>
+      </c>
+      <c r="F40" s="22">
         <v>42.707999999999998</v>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="22">
         <v>50.598999999999997</v>
       </c>
-      <c r="H40" s="21">
+      <c r="H40" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20">
+      <c r="A41" s="22">
         <v>47.59</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="22">
         <v>10.672000000000001</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="22">
         <v>43.67</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="22">
         <v>51.51</v>
       </c>
-      <c r="E41" s="21">
-        <v>1</v>
-      </c>
-      <c r="F41" s="20">
+      <c r="E41" s="23">
+        <v>1</v>
+      </c>
+      <c r="F41" s="22">
         <v>43.185000000000002</v>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="22">
         <v>51.994999999999997</v>
       </c>
-      <c r="H41" s="21">
+      <c r="H41" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="20">
+      <c r="A42" s="22">
         <v>48.357999999999997</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="22">
         <v>9.6059999999999999</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="22">
         <v>44.438000000000002</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="22">
         <v>52.277999999999999</v>
       </c>
-      <c r="E42" s="21">
-        <v>1</v>
-      </c>
-      <c r="F42" s="20">
+      <c r="E42" s="23">
+        <v>1</v>
+      </c>
+      <c r="F42" s="22">
         <v>44.393000000000001</v>
       </c>
-      <c r="G42" s="20">
+      <c r="G42" s="22">
         <v>52.323999999999998</v>
       </c>
-      <c r="H42" s="21">
+      <c r="H42" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20">
+      <c r="A43" s="22">
         <v>49.445999999999998</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="22">
         <v>12.071</v>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="22">
         <v>45.526000000000003</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="22">
         <v>53.366</v>
       </c>
-      <c r="E43" s="21">
-        <v>1</v>
-      </c>
-      <c r="F43" s="20">
+      <c r="E43" s="23">
+        <v>1</v>
+      </c>
+      <c r="F43" s="22">
         <v>44.463999999999999</v>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="22">
         <v>54.429000000000002</v>
       </c>
-      <c r="H43" s="21">
+      <c r="H43" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="20">
+      <c r="A44" s="22">
         <v>47.527999999999999</v>
       </c>
-      <c r="B44" s="20">
+      <c r="B44" s="22">
         <v>9.7479999999999993</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="22">
         <v>43.607999999999997</v>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="22">
         <v>51.448</v>
       </c>
-      <c r="E44" s="21">
-        <v>1</v>
-      </c>
-      <c r="F44" s="20">
+      <c r="E44" s="23">
+        <v>1</v>
+      </c>
+      <c r="F44" s="22">
         <v>43.503999999999998</v>
       </c>
-      <c r="G44" s="20">
+      <c r="G44" s="22">
         <v>51.552</v>
       </c>
-      <c r="H44" s="21">
+      <c r="H44" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20">
+      <c r="A45" s="22">
         <v>46.244</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45" s="22">
         <v>7.3970000000000002</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C45" s="22">
         <v>42.323999999999998</v>
       </c>
-      <c r="D45" s="20">
+      <c r="D45" s="22">
         <v>50.164000000000001</v>
       </c>
-      <c r="E45" s="21">
-        <v>1</v>
-      </c>
-      <c r="F45" s="20">
+      <c r="E45" s="23">
+        <v>1</v>
+      </c>
+      <c r="F45" s="22">
         <v>43.191000000000003</v>
       </c>
-      <c r="G45" s="20">
+      <c r="G45" s="22">
         <v>49.296999999999997</v>
       </c>
-      <c r="H45" s="21">
+      <c r="H45" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
+      <c r="A46" s="22">
         <v>48.274999999999999</v>
       </c>
-      <c r="B46" s="20">
+      <c r="B46" s="22">
         <v>9.2050000000000001</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C46" s="22">
         <v>44.354999999999997</v>
       </c>
-      <c r="D46" s="20">
+      <c r="D46" s="22">
         <v>52.195</v>
       </c>
-      <c r="E46" s="21">
-        <v>1</v>
-      </c>
-      <c r="F46" s="20">
+      <c r="E46" s="23">
+        <v>1</v>
+      </c>
+      <c r="F46" s="22">
         <v>44.475999999999999</v>
       </c>
-      <c r="G46" s="20">
+      <c r="G46" s="22">
         <v>52.075000000000003</v>
       </c>
-      <c r="H46" s="21">
+      <c r="H46" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="20">
+      <c r="A47" s="22">
         <v>42.777999999999999</v>
       </c>
-      <c r="B47" s="20">
+      <c r="B47" s="22">
         <v>9.7850000000000001</v>
       </c>
-      <c r="C47" s="20">
+      <c r="C47" s="22">
         <v>38.857999999999997</v>
       </c>
-      <c r="D47" s="20">
+      <c r="D47" s="22">
         <v>46.698</v>
       </c>
-      <c r="E47" s="21">
+      <c r="E47" s="23">
         <v>0</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="22">
         <v>38.738999999999997</v>
       </c>
-      <c r="G47" s="20">
+      <c r="G47" s="22">
         <v>46.817</v>
       </c>
-      <c r="H47" s="21">
+      <c r="H47" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="20">
+      <c r="A48" s="22">
         <v>46.618000000000002</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="22">
         <v>10.548999999999999</v>
       </c>
-      <c r="C48" s="20">
+      <c r="C48" s="22">
         <v>42.698</v>
       </c>
-      <c r="D48" s="20">
+      <c r="D48" s="22">
         <v>50.537999999999997</v>
       </c>
-      <c r="E48" s="21">
-        <v>1</v>
-      </c>
-      <c r="F48" s="20">
+      <c r="E48" s="23">
+        <v>1</v>
+      </c>
+      <c r="F48" s="22">
         <v>42.264000000000003</v>
       </c>
-      <c r="G48" s="20">
+      <c r="G48" s="22">
         <v>50.972000000000001</v>
       </c>
-      <c r="H48" s="21">
+      <c r="H48" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="20">
+      <c r="A49" s="22">
         <v>49.11</v>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="22">
         <v>11.172000000000001</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C49" s="22">
         <v>45.19</v>
       </c>
-      <c r="D49" s="20">
+      <c r="D49" s="22">
         <v>53.03</v>
       </c>
-      <c r="E49" s="21">
-        <v>1</v>
-      </c>
-      <c r="F49" s="20">
+      <c r="E49" s="23">
+        <v>1</v>
+      </c>
+      <c r="F49" s="22">
         <v>44.499000000000002</v>
       </c>
-      <c r="G49" s="20">
+      <c r="G49" s="22">
         <v>53.722000000000001</v>
       </c>
-      <c r="H49" s="21">
+      <c r="H49" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="20">
+      <c r="A50" s="22">
         <v>45.954999999999998</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="22">
         <v>9.4429999999999996</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C50" s="22">
         <v>42.034999999999997</v>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="22">
         <v>49.875</v>
       </c>
-      <c r="E50" s="21">
-        <v>1</v>
-      </c>
-      <c r="F50" s="20">
+      <c r="E50" s="23">
+        <v>1</v>
+      </c>
+      <c r="F50" s="22">
         <v>42.057000000000002</v>
       </c>
-      <c r="G50" s="20">
+      <c r="G50" s="22">
         <v>49.851999999999997</v>
       </c>
-      <c r="H50" s="21">
+      <c r="H50" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20">
+      <c r="A51" s="22">
         <v>49.514000000000003</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="22">
         <v>11.587</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="22">
         <v>45.594000000000001</v>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="22">
         <v>53.433999999999997</v>
       </c>
-      <c r="E51" s="21">
-        <v>1</v>
-      </c>
-      <c r="F51" s="20">
+      <c r="E51" s="23">
+        <v>1</v>
+      </c>
+      <c r="F51" s="22">
         <v>44.731000000000002</v>
       </c>
-      <c r="G51" s="20">
+      <c r="G51" s="22">
         <v>54.296999999999997</v>
       </c>
-      <c r="H51" s="21">
+      <c r="H51" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="20">
+      <c r="A52" s="22">
         <v>45.094000000000001</v>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="22">
         <v>11.191000000000001</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="22">
         <v>41.173999999999999</v>
       </c>
-      <c r="D52" s="20">
+      <c r="D52" s="22">
         <v>49.014000000000003</v>
       </c>
-      <c r="E52" s="21">
-        <v>1</v>
-      </c>
-      <c r="F52" s="20">
+      <c r="E52" s="23">
+        <v>1</v>
+      </c>
+      <c r="F52" s="22">
         <v>40.473999999999997</v>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="22">
         <v>49.713000000000001</v>
       </c>
-      <c r="H52" s="21">
+      <c r="H52" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="20">
+      <c r="A53" s="22">
         <v>43.392000000000003</v>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="22">
         <v>10.513</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="22">
         <v>39.472000000000001</v>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="22">
         <v>47.311999999999998</v>
       </c>
-      <c r="E53" s="21">
-        <v>1</v>
-      </c>
-      <c r="F53" s="20">
+      <c r="E53" s="23">
+        <v>1</v>
+      </c>
+      <c r="F53" s="22">
         <v>39.052</v>
       </c>
-      <c r="G53" s="20">
+      <c r="G53" s="22">
         <v>47.731000000000002</v>
       </c>
-      <c r="H53" s="21">
+      <c r="H53" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="20">
+      <c r="A54" s="22">
         <v>49.338000000000001</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="22">
         <v>11.343999999999999</v>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="22">
         <v>45.417999999999999</v>
       </c>
-      <c r="D54" s="20">
+      <c r="D54" s="22">
         <v>53.258000000000003</v>
       </c>
-      <c r="E54" s="21">
-        <v>1</v>
-      </c>
-      <c r="F54" s="20">
+      <c r="E54" s="23">
+        <v>1</v>
+      </c>
+      <c r="F54" s="22">
         <v>44.655000000000001</v>
       </c>
-      <c r="G54" s="20">
+      <c r="G54" s="22">
         <v>54.021000000000001</v>
       </c>
-      <c r="H54" s="21">
+      <c r="H54" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="20">
+      <c r="A55" s="22">
         <v>44.686</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="22">
         <v>9.1959999999999997</v>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="22">
         <v>40.765999999999998</v>
       </c>
-      <c r="D55" s="20">
+      <c r="D55" s="22">
         <v>48.606000000000002</v>
       </c>
-      <c r="E55" s="21">
-        <v>1</v>
-      </c>
-      <c r="F55" s="20">
+      <c r="E55" s="23">
+        <v>1</v>
+      </c>
+      <c r="F55" s="22">
         <v>40.89</v>
       </c>
-      <c r="G55" s="20">
+      <c r="G55" s="22">
         <v>48.481999999999999</v>
       </c>
-      <c r="H55" s="21">
+      <c r="H55" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="20">
+      <c r="A56" s="22">
         <v>46.701999999999998</v>
       </c>
-      <c r="B56" s="20">
+      <c r="B56" s="22">
         <v>11.601000000000001</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="22">
         <v>42.781999999999996</v>
       </c>
-      <c r="D56" s="20">
+      <c r="D56" s="22">
         <v>50.622</v>
       </c>
-      <c r="E56" s="21">
-        <v>1</v>
-      </c>
-      <c r="F56" s="20">
+      <c r="E56" s="23">
+        <v>1</v>
+      </c>
+      <c r="F56" s="22">
         <v>41.912999999999997</v>
       </c>
-      <c r="G56" s="20">
+      <c r="G56" s="22">
         <v>51.49</v>
       </c>
-      <c r="H56" s="21">
+      <c r="H56" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="20">
+      <c r="A57" s="22">
         <v>47.116999999999997</v>
       </c>
-      <c r="B57" s="20">
+      <c r="B57" s="22">
         <v>8.1780000000000008</v>
       </c>
-      <c r="C57" s="20">
+      <c r="C57" s="22">
         <v>43.198</v>
       </c>
-      <c r="D57" s="20">
+      <c r="D57" s="22">
         <v>51.036999999999999</v>
       </c>
-      <c r="E57" s="21">
-        <v>1</v>
-      </c>
-      <c r="F57" s="20">
+      <c r="E57" s="23">
+        <v>1</v>
+      </c>
+      <c r="F57" s="22">
         <v>43.741999999999997</v>
       </c>
-      <c r="G57" s="20">
+      <c r="G57" s="22">
         <v>50.493000000000002</v>
       </c>
-      <c r="H57" s="21">
+      <c r="H57" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="20">
+      <c r="A58" s="22">
         <v>46.862000000000002</v>
       </c>
-      <c r="B58" s="20">
+      <c r="B58" s="22">
         <v>8.9860000000000007</v>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="22">
         <v>42.942</v>
       </c>
-      <c r="D58" s="20">
+      <c r="D58" s="22">
         <v>50.781999999999996</v>
       </c>
-      <c r="E58" s="21">
-        <v>1</v>
-      </c>
-      <c r="F58" s="20">
+      <c r="E58" s="23">
+        <v>1</v>
+      </c>
+      <c r="F58" s="22">
         <v>43.152999999999999</v>
       </c>
-      <c r="G58" s="20">
+      <c r="G58" s="22">
         <v>50.570999999999998</v>
       </c>
-      <c r="H58" s="21">
+      <c r="H58" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="20">
+      <c r="A59" s="22">
         <v>49.780999999999999</v>
       </c>
-      <c r="B59" s="20">
+      <c r="B59" s="22">
         <v>10.173999999999999</v>
       </c>
-      <c r="C59" s="20">
+      <c r="C59" s="22">
         <v>45.860999999999997</v>
       </c>
-      <c r="D59" s="20">
+      <c r="D59" s="22">
         <v>53.701000000000001</v>
       </c>
-      <c r="E59" s="21">
-        <v>1</v>
-      </c>
-      <c r="F59" s="20">
+      <c r="E59" s="23">
+        <v>1</v>
+      </c>
+      <c r="F59" s="22">
         <v>45.582000000000001</v>
       </c>
-      <c r="G59" s="20">
+      <c r="G59" s="22">
         <v>53.981000000000002</v>
       </c>
-      <c r="H59" s="21">
+      <c r="H59" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="20">
+      <c r="A60" s="22">
         <v>49.03</v>
       </c>
-      <c r="B60" s="20">
+      <c r="B60" s="22">
         <v>11.259</v>
       </c>
-      <c r="C60" s="20">
+      <c r="C60" s="22">
         <v>45.11</v>
       </c>
-      <c r="D60" s="20">
+      <c r="D60" s="22">
         <v>52.95</v>
       </c>
-      <c r="E60" s="21">
-        <v>1</v>
-      </c>
-      <c r="F60" s="20">
+      <c r="E60" s="23">
+        <v>1</v>
+      </c>
+      <c r="F60" s="22">
         <v>44.381999999999998</v>
       </c>
-      <c r="G60" s="20">
+      <c r="G60" s="22">
         <v>53.677999999999997</v>
       </c>
-      <c r="H60" s="21">
+      <c r="H60" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="20">
+      <c r="A61" s="22">
         <v>45.124000000000002</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="22">
         <v>9.0020000000000007</v>
       </c>
-      <c r="C61" s="20">
+      <c r="C61" s="22">
         <v>41.204000000000001</v>
       </c>
-      <c r="D61" s="20">
+      <c r="D61" s="22">
         <v>49.043999999999997</v>
       </c>
-      <c r="E61" s="21">
-        <v>1</v>
-      </c>
-      <c r="F61" s="20">
+      <c r="E61" s="23">
+        <v>1</v>
+      </c>
+      <c r="F61" s="22">
         <v>41.408000000000001</v>
       </c>
-      <c r="G61" s="20">
+      <c r="G61" s="22">
         <v>48.838999999999999</v>
       </c>
-      <c r="H61" s="21">
+      <c r="H61" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="20">
+      <c r="A62" s="22">
         <v>46.326000000000001</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B62" s="22">
         <v>10.5</v>
       </c>
-      <c r="C62" s="20">
+      <c r="C62" s="22">
         <v>42.405999999999999</v>
       </c>
-      <c r="D62" s="20">
+      <c r="D62" s="22">
         <v>50.246000000000002</v>
       </c>
-      <c r="E62" s="21">
-        <v>1</v>
-      </c>
-      <c r="F62" s="20">
+      <c r="E62" s="23">
+        <v>1</v>
+      </c>
+      <c r="F62" s="22">
         <v>41.991999999999997</v>
       </c>
-      <c r="G62" s="20">
+      <c r="G62" s="22">
         <v>50.66</v>
       </c>
-      <c r="H62" s="21">
+      <c r="H62" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="20">
+      <c r="A63" s="22">
         <v>47.454000000000001</v>
       </c>
-      <c r="B63" s="20">
+      <c r="B63" s="22">
         <v>7.2919999999999998</v>
       </c>
-      <c r="C63" s="20">
+      <c r="C63" s="22">
         <v>43.533999999999999</v>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="22">
         <v>51.374000000000002</v>
       </c>
-      <c r="E63" s="21">
-        <v>1</v>
-      </c>
-      <c r="F63" s="20">
+      <c r="E63" s="23">
+        <v>1</v>
+      </c>
+      <c r="F63" s="22">
         <v>44.444000000000003</v>
       </c>
-      <c r="G63" s="20">
+      <c r="G63" s="22">
         <v>50.463999999999999</v>
       </c>
-      <c r="H63" s="21">
+      <c r="H63" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="20">
+      <c r="A64" s="22">
         <v>46.588000000000001</v>
       </c>
-      <c r="B64" s="20">
+      <c r="B64" s="22">
         <v>8.5579999999999998</v>
       </c>
-      <c r="C64" s="20">
+      <c r="C64" s="22">
         <v>42.667999999999999</v>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="22">
         <v>50.508000000000003</v>
       </c>
-      <c r="E64" s="21">
-        <v>1</v>
-      </c>
-      <c r="F64" s="20">
+      <c r="E64" s="23">
+        <v>1</v>
+      </c>
+      <c r="F64" s="22">
         <v>43.055999999999997</v>
       </c>
-      <c r="G64" s="20">
+      <c r="G64" s="22">
         <v>50.121000000000002</v>
       </c>
-      <c r="H64" s="21">
+      <c r="H64" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="20">
+      <c r="A65" s="22">
         <v>44.643000000000001</v>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="22">
         <v>9.8170000000000002</v>
       </c>
-      <c r="C65" s="20">
+      <c r="C65" s="22">
         <v>40.722999999999999</v>
       </c>
-      <c r="D65" s="20">
+      <c r="D65" s="22">
         <v>48.563000000000002</v>
       </c>
-      <c r="E65" s="21">
-        <v>1</v>
-      </c>
-      <c r="F65" s="20">
+      <c r="E65" s="23">
+        <v>1</v>
+      </c>
+      <c r="F65" s="22">
         <v>40.591000000000001</v>
       </c>
-      <c r="G65" s="20">
+      <c r="G65" s="22">
         <v>48.695</v>
       </c>
-      <c r="H65" s="21">
+      <c r="H65" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="20">
+      <c r="A66" s="22">
         <v>47.640999999999998</v>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="22">
         <v>9.4689999999999994</v>
       </c>
-      <c r="C66" s="20">
+      <c r="C66" s="22">
         <v>43.720999999999997</v>
       </c>
-      <c r="D66" s="20">
+      <c r="D66" s="22">
         <v>51.561</v>
       </c>
-      <c r="E66" s="21">
-        <v>1</v>
-      </c>
-      <c r="F66" s="20">
+      <c r="E66" s="23">
+        <v>1</v>
+      </c>
+      <c r="F66" s="22">
         <v>43.731999999999999</v>
       </c>
-      <c r="G66" s="20">
+      <c r="G66" s="22">
         <v>51.548999999999999</v>
       </c>
-      <c r="H66" s="21">
+      <c r="H66" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="20">
+      <c r="A67" s="22">
         <v>47.969000000000001</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="22">
         <v>9.1579999999999995</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="22">
         <v>44.048999999999999</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="22">
         <v>51.889000000000003</v>
       </c>
-      <c r="E67" s="21">
-        <v>1</v>
-      </c>
-      <c r="F67" s="20">
+      <c r="E67" s="23">
+        <v>1</v>
+      </c>
+      <c r="F67" s="22">
         <v>44.189</v>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="22">
         <v>51.749000000000002</v>
       </c>
-      <c r="H67" s="21">
+      <c r="H67" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="20">
+      <c r="A68" s="22">
         <v>47.911000000000001</v>
       </c>
-      <c r="B68" s="20">
+      <c r="B68" s="22">
         <v>8.8040000000000003</v>
       </c>
-      <c r="C68" s="20">
+      <c r="C68" s="22">
         <v>43.991</v>
       </c>
-      <c r="D68" s="20">
+      <c r="D68" s="22">
         <v>51.831000000000003</v>
       </c>
-      <c r="E68" s="21">
-        <v>1</v>
-      </c>
-      <c r="F68" s="20">
+      <c r="E68" s="23">
+        <v>1</v>
+      </c>
+      <c r="F68" s="22">
         <v>44.276000000000003</v>
       </c>
-      <c r="G68" s="20">
+      <c r="G68" s="22">
         <v>51.545000000000002</v>
       </c>
-      <c r="H68" s="21">
+      <c r="H68" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="20">
+      <c r="A69" s="22">
         <v>46.131</v>
       </c>
-      <c r="B69" s="20">
+      <c r="B69" s="22">
         <v>12.099</v>
       </c>
-      <c r="C69" s="20">
+      <c r="C69" s="22">
         <v>42.210999999999999</v>
       </c>
-      <c r="D69" s="20">
+      <c r="D69" s="22">
         <v>50.051000000000002</v>
       </c>
-      <c r="E69" s="21">
-        <v>1</v>
-      </c>
-      <c r="F69" s="20">
+      <c r="E69" s="23">
+        <v>1</v>
+      </c>
+      <c r="F69" s="22">
         <v>41.137</v>
       </c>
-      <c r="G69" s="20">
+      <c r="G69" s="22">
         <v>51.125</v>
       </c>
-      <c r="H69" s="21">
+      <c r="H69" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="20">
+      <c r="A70" s="22">
         <v>45.573</v>
       </c>
-      <c r="B70" s="20">
+      <c r="B70" s="22">
         <v>12.728</v>
       </c>
-      <c r="C70" s="20">
+      <c r="C70" s="22">
         <v>41.654000000000003</v>
       </c>
-      <c r="D70" s="20">
+      <c r="D70" s="22">
         <v>49.493000000000002</v>
       </c>
-      <c r="E70" s="21">
-        <v>1</v>
-      </c>
-      <c r="F70" s="20">
+      <c r="E70" s="23">
+        <v>1</v>
+      </c>
+      <c r="F70" s="22">
         <v>40.32</v>
       </c>
-      <c r="G70" s="20">
+      <c r="G70" s="22">
         <v>50.826999999999998</v>
       </c>
-      <c r="H70" s="21">
+      <c r="H70" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="20">
+      <c r="A71" s="22">
         <v>45.593000000000004</v>
       </c>
-      <c r="B71" s="20">
+      <c r="B71" s="22">
         <v>9.4879999999999995</v>
       </c>
-      <c r="C71" s="20">
+      <c r="C71" s="22">
         <v>41.673000000000002</v>
       </c>
-      <c r="D71" s="20">
+      <c r="D71" s="22">
         <v>49.512999999999998</v>
       </c>
-      <c r="E71" s="21">
-        <v>1</v>
-      </c>
-      <c r="F71" s="20">
+      <c r="E71" s="23">
+        <v>1</v>
+      </c>
+      <c r="F71" s="22">
         <v>41.677</v>
       </c>
-      <c r="G71" s="20">
+      <c r="G71" s="22">
         <v>49.509</v>
       </c>
-      <c r="H71" s="21">
+      <c r="H71" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="20">
+      <c r="A72" s="22">
         <v>46.265999999999998</v>
       </c>
-      <c r="B72" s="20">
+      <c r="B72" s="22">
         <v>9.1839999999999993</v>
       </c>
-      <c r="C72" s="20">
+      <c r="C72" s="22">
         <v>42.345999999999997</v>
       </c>
-      <c r="D72" s="20">
+      <c r="D72" s="22">
         <v>50.186</v>
       </c>
-      <c r="E72" s="21">
-        <v>1</v>
-      </c>
-      <c r="F72" s="20">
+      <c r="E72" s="23">
+        <v>1</v>
+      </c>
+      <c r="F72" s="22">
         <v>42.475000000000001</v>
       </c>
-      <c r="G72" s="20">
+      <c r="G72" s="22">
         <v>50.057000000000002</v>
       </c>
-      <c r="H72" s="21">
+      <c r="H72" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="20">
+      <c r="A73" s="22">
         <v>46.097999999999999</v>
       </c>
-      <c r="B73" s="20">
+      <c r="B73" s="22">
         <v>8.4649999999999999</v>
       </c>
-      <c r="C73" s="20">
+      <c r="C73" s="22">
         <v>42.177999999999997</v>
       </c>
-      <c r="D73" s="20">
+      <c r="D73" s="22">
         <v>50.018000000000001</v>
       </c>
-      <c r="E73" s="21">
-        <v>1</v>
-      </c>
-      <c r="F73" s="20">
+      <c r="E73" s="23">
+        <v>1</v>
+      </c>
+      <c r="F73" s="22">
         <v>42.603999999999999</v>
       </c>
-      <c r="G73" s="20">
+      <c r="G73" s="22">
         <v>49.593000000000004</v>
       </c>
-      <c r="H73" s="21">
+      <c r="H73" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="20">
+      <c r="A74" s="22">
         <v>47.094000000000001</v>
       </c>
-      <c r="B74" s="20">
+      <c r="B74" s="22">
         <v>8.6259999999999994</v>
       </c>
-      <c r="C74" s="20">
+      <c r="C74" s="22">
         <v>43.173999999999999</v>
       </c>
-      <c r="D74" s="20">
+      <c r="D74" s="22">
         <v>51.014000000000003</v>
       </c>
-      <c r="E74" s="21">
-        <v>1</v>
-      </c>
-      <c r="F74" s="20">
+      <c r="E74" s="23">
+        <v>1</v>
+      </c>
+      <c r="F74" s="22">
         <v>43.533999999999999</v>
       </c>
-      <c r="G74" s="20">
+      <c r="G74" s="22">
         <v>50.655000000000001</v>
       </c>
-      <c r="H74" s="21">
+      <c r="H74" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="20">
+      <c r="A75" s="22">
         <v>41.555</v>
       </c>
-      <c r="B75" s="20">
+      <c r="B75" s="22">
         <v>11.946999999999999</v>
       </c>
-      <c r="C75" s="20">
+      <c r="C75" s="22">
         <v>37.634999999999998</v>
       </c>
-      <c r="D75" s="20">
+      <c r="D75" s="22">
         <v>45.475000000000001</v>
       </c>
-      <c r="E75" s="21">
+      <c r="E75" s="23">
         <v>0</v>
       </c>
-      <c r="F75" s="20">
+      <c r="F75" s="22">
         <v>36.624000000000002</v>
       </c>
-      <c r="G75" s="20">
+      <c r="G75" s="22">
         <v>46.487000000000002</v>
       </c>
-      <c r="H75" s="21">
+      <c r="H75" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="20">
+      <c r="A76" s="22">
         <v>45.962000000000003</v>
       </c>
-      <c r="B76" s="20">
+      <c r="B76" s="22">
         <v>8.3089999999999993</v>
       </c>
-      <c r="C76" s="20">
+      <c r="C76" s="22">
         <v>42.042000000000002</v>
       </c>
-      <c r="D76" s="20">
+      <c r="D76" s="22">
         <v>49.881999999999998</v>
       </c>
-      <c r="E76" s="21">
-        <v>1</v>
-      </c>
-      <c r="F76" s="20">
+      <c r="E76" s="23">
+        <v>1</v>
+      </c>
+      <c r="F76" s="22">
         <v>42.531999999999996</v>
       </c>
-      <c r="G76" s="20">
+      <c r="G76" s="22">
         <v>49.390999999999998</v>
       </c>
-      <c r="H76" s="21">
+      <c r="H76" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="20">
+      <c r="A77" s="22">
         <v>45.767000000000003</v>
       </c>
-      <c r="B77" s="20">
+      <c r="B77" s="22">
         <v>12.423</v>
       </c>
-      <c r="C77" s="20">
+      <c r="C77" s="22">
         <v>41.847000000000001</v>
       </c>
-      <c r="D77" s="20">
+      <c r="D77" s="22">
         <v>49.686999999999998</v>
       </c>
-      <c r="E77" s="21">
-        <v>1</v>
-      </c>
-      <c r="F77" s="20">
+      <c r="E77" s="23">
+        <v>1</v>
+      </c>
+      <c r="F77" s="22">
         <v>40.639000000000003</v>
       </c>
-      <c r="G77" s="20">
+      <c r="G77" s="22">
         <v>50.895000000000003</v>
       </c>
-      <c r="H77" s="21">
+      <c r="H77" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="20">
+      <c r="A78" s="22">
         <v>44.05</v>
       </c>
-      <c r="B78" s="20">
+      <c r="B78" s="22">
         <v>9.3849999999999998</v>
       </c>
-      <c r="C78" s="20">
+      <c r="C78" s="22">
         <v>40.130000000000003</v>
       </c>
-      <c r="D78" s="20">
+      <c r="D78" s="22">
         <v>47.97</v>
       </c>
-      <c r="E78" s="21">
-        <v>1</v>
-      </c>
-      <c r="F78" s="20">
+      <c r="E78" s="23">
+        <v>1</v>
+      </c>
+      <c r="F78" s="22">
         <v>40.176000000000002</v>
       </c>
-      <c r="G78" s="20">
+      <c r="G78" s="22">
         <v>47.923999999999999</v>
       </c>
-      <c r="H78" s="21">
+      <c r="H78" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="20">
+      <c r="A79" s="22">
         <v>46.186999999999998</v>
       </c>
-      <c r="B79" s="20">
+      <c r="B79" s="22">
         <v>11.891999999999999</v>
       </c>
-      <c r="C79" s="20">
+      <c r="C79" s="22">
         <v>42.267000000000003</v>
       </c>
-      <c r="D79" s="20">
+      <c r="D79" s="22">
         <v>50.106000000000002</v>
       </c>
-      <c r="E79" s="21">
-        <v>1</v>
-      </c>
-      <c r="F79" s="20">
+      <c r="E79" s="23">
+        <v>1</v>
+      </c>
+      <c r="F79" s="22">
         <v>41.277999999999999</v>
       </c>
-      <c r="G79" s="20">
+      <c r="G79" s="22">
         <v>51.094999999999999</v>
       </c>
-      <c r="H79" s="21">
+      <c r="H79" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="20">
+      <c r="A80" s="22">
         <v>49.027000000000001</v>
       </c>
-      <c r="B80" s="20">
+      <c r="B80" s="22">
         <v>10.33</v>
       </c>
-      <c r="C80" s="20">
+      <c r="C80" s="22">
         <v>45.106999999999999</v>
       </c>
-      <c r="D80" s="20">
+      <c r="D80" s="22">
         <v>52.947000000000003</v>
       </c>
-      <c r="E80" s="21">
-        <v>1</v>
-      </c>
-      <c r="F80" s="20">
+      <c r="E80" s="23">
+        <v>1</v>
+      </c>
+      <c r="F80" s="22">
         <v>44.762999999999998</v>
       </c>
-      <c r="G80" s="20">
+      <c r="G80" s="22">
         <v>53.290999999999997</v>
       </c>
-      <c r="H80" s="21">
+      <c r="H80" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="20">
+      <c r="A81" s="22">
         <v>47.564</v>
       </c>
-      <c r="B81" s="20">
+      <c r="B81" s="22">
         <v>8.6969999999999992</v>
       </c>
-      <c r="C81" s="20">
+      <c r="C81" s="22">
         <v>43.643999999999998</v>
       </c>
-      <c r="D81" s="20">
+      <c r="D81" s="22">
         <v>51.484000000000002</v>
       </c>
-      <c r="E81" s="21">
-        <v>1</v>
-      </c>
-      <c r="F81" s="20">
+      <c r="E81" s="23">
+        <v>1</v>
+      </c>
+      <c r="F81" s="22">
         <v>43.973999999999997</v>
       </c>
-      <c r="G81" s="20">
+      <c r="G81" s="22">
         <v>51.154000000000003</v>
       </c>
-      <c r="H81" s="21">
+      <c r="H81" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="20">
+      <c r="A82" s="22">
         <v>47.042000000000002</v>
       </c>
-      <c r="B82" s="20">
+      <c r="B82" s="22">
         <v>8.5709999999999997</v>
       </c>
-      <c r="C82" s="20">
+      <c r="C82" s="22">
         <v>43.122</v>
       </c>
-      <c r="D82" s="20">
+      <c r="D82" s="22">
         <v>50.962000000000003</v>
       </c>
-      <c r="E82" s="21">
-        <v>1</v>
-      </c>
-      <c r="F82" s="20">
+      <c r="E82" s="23">
+        <v>1</v>
+      </c>
+      <c r="F82" s="22">
         <v>43.503999999999998</v>
       </c>
-      <c r="G82" s="20">
+      <c r="G82" s="22">
         <v>50.58</v>
       </c>
-      <c r="H82" s="21">
+      <c r="H82" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="20">
+      <c r="A83" s="22">
         <v>46.377000000000002</v>
       </c>
-      <c r="B83" s="20">
+      <c r="B83" s="22">
         <v>9.9809999999999999</v>
       </c>
-      <c r="C83" s="20">
+      <c r="C83" s="22">
         <v>42.457000000000001</v>
       </c>
-      <c r="D83" s="20">
+      <c r="D83" s="22">
         <v>50.295999999999999</v>
       </c>
-      <c r="E83" s="21">
-        <v>1</v>
-      </c>
-      <c r="F83" s="20">
+      <c r="E83" s="23">
+        <v>1</v>
+      </c>
+      <c r="F83" s="22">
         <v>42.256999999999998</v>
       </c>
-      <c r="G83" s="20">
+      <c r="G83" s="22">
         <v>50.496000000000002</v>
       </c>
-      <c r="H83" s="21">
+      <c r="H83" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="20">
+      <c r="A84" s="22">
         <v>47.323999999999998</v>
       </c>
-      <c r="B84" s="20">
+      <c r="B84" s="22">
         <v>10.551</v>
       </c>
-      <c r="C84" s="20">
+      <c r="C84" s="22">
         <v>43.404000000000003</v>
       </c>
-      <c r="D84" s="20">
+      <c r="D84" s="22">
         <v>51.244</v>
       </c>
-      <c r="E84" s="21">
-        <v>1</v>
-      </c>
-      <c r="F84" s="20">
+      <c r="E84" s="23">
+        <v>1</v>
+      </c>
+      <c r="F84" s="22">
         <v>42.969000000000001</v>
       </c>
-      <c r="G84" s="20">
+      <c r="G84" s="22">
         <v>51.679000000000002</v>
       </c>
-      <c r="H84" s="21">
+      <c r="H84" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="20">
+      <c r="A85" s="22">
         <v>44.825000000000003</v>
       </c>
-      <c r="B85" s="20">
+      <c r="B85" s="22">
         <v>8.3030000000000008</v>
       </c>
-      <c r="C85" s="20">
+      <c r="C85" s="22">
         <v>40.905000000000001</v>
       </c>
-      <c r="D85" s="20">
+      <c r="D85" s="22">
         <v>48.744999999999997</v>
       </c>
-      <c r="E85" s="21">
-        <v>1</v>
-      </c>
-      <c r="F85" s="20">
+      <c r="E85" s="23">
+        <v>1</v>
+      </c>
+      <c r="F85" s="22">
         <v>41.398000000000003</v>
       </c>
-      <c r="G85" s="20">
+      <c r="G85" s="22">
         <v>48.252000000000002</v>
       </c>
-      <c r="H85" s="21">
+      <c r="H85" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="20">
+      <c r="A86" s="22">
         <v>48.04</v>
       </c>
-      <c r="B86" s="20">
+      <c r="B86" s="22">
         <v>8.4580000000000002</v>
       </c>
-      <c r="C86" s="20">
+      <c r="C86" s="22">
         <v>44.12</v>
       </c>
-      <c r="D86" s="20">
+      <c r="D86" s="22">
         <v>51.96</v>
       </c>
-      <c r="E86" s="21">
-        <v>1</v>
-      </c>
-      <c r="F86" s="20">
+      <c r="E86" s="23">
+        <v>1</v>
+      </c>
+      <c r="F86" s="22">
         <v>44.548999999999999</v>
       </c>
-      <c r="G86" s="20">
+      <c r="G86" s="22">
         <v>51.530999999999999</v>
       </c>
-      <c r="H86" s="21">
+      <c r="H86" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="20">
+      <c r="A87" s="22">
         <v>47.393000000000001</v>
       </c>
-      <c r="B87" s="20">
+      <c r="B87" s="22">
         <v>8.9149999999999991</v>
       </c>
-      <c r="C87" s="20">
+      <c r="C87" s="22">
         <v>43.472999999999999</v>
       </c>
-      <c r="D87" s="20">
+      <c r="D87" s="22">
         <v>51.313000000000002</v>
       </c>
-      <c r="E87" s="21">
-        <v>1</v>
-      </c>
-      <c r="F87" s="20">
+      <c r="E87" s="23">
+        <v>1</v>
+      </c>
+      <c r="F87" s="22">
         <v>43.713999999999999</v>
       </c>
-      <c r="G87" s="20">
+      <c r="G87" s="22">
         <v>51.073</v>
       </c>
-      <c r="H87" s="21">
+      <c r="H87" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="20">
+      <c r="A88" s="22">
         <v>45.924999999999997</v>
       </c>
-      <c r="B88" s="20">
+      <c r="B88" s="22">
         <v>9.2349999999999994</v>
       </c>
-      <c r="C88" s="20">
+      <c r="C88" s="22">
         <v>42.005000000000003</v>
       </c>
-      <c r="D88" s="20">
+      <c r="D88" s="22">
         <v>49.844999999999999</v>
       </c>
-      <c r="E88" s="21">
-        <v>1</v>
-      </c>
-      <c r="F88" s="20">
+      <c r="E88" s="23">
+        <v>1</v>
+      </c>
+      <c r="F88" s="22">
         <v>42.113</v>
       </c>
-      <c r="G88" s="20">
+      <c r="G88" s="22">
         <v>49.737000000000002</v>
       </c>
-      <c r="H88" s="21">
+      <c r="H88" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="20">
+      <c r="A89" s="22">
         <v>45.265000000000001</v>
       </c>
-      <c r="B89" s="20">
+      <c r="B89" s="22">
         <v>9.7550000000000008</v>
       </c>
-      <c r="C89" s="20">
+      <c r="C89" s="22">
         <v>41.344999999999999</v>
       </c>
-      <c r="D89" s="20">
+      <c r="D89" s="22">
         <v>49.185000000000002</v>
       </c>
-      <c r="E89" s="21">
-        <v>1</v>
-      </c>
-      <c r="F89" s="20">
+      <c r="E89" s="23">
+        <v>1</v>
+      </c>
+      <c r="F89" s="22">
         <v>41.238</v>
       </c>
-      <c r="G89" s="20">
+      <c r="G89" s="22">
         <v>49.290999999999997</v>
       </c>
-      <c r="H89" s="21">
+      <c r="H89" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="20">
+      <c r="A90" s="22">
         <v>48.213999999999999</v>
       </c>
-      <c r="B90" s="20">
+      <c r="B90" s="22">
         <v>10.657999999999999</v>
       </c>
-      <c r="C90" s="20">
+      <c r="C90" s="22">
         <v>44.293999999999997</v>
       </c>
-      <c r="D90" s="20">
+      <c r="D90" s="22">
         <v>52.134</v>
       </c>
-      <c r="E90" s="21">
-        <v>1</v>
-      </c>
-      <c r="F90" s="20">
+      <c r="E90" s="23">
+        <v>1</v>
+      </c>
+      <c r="F90" s="22">
         <v>43.814999999999998</v>
       </c>
-      <c r="G90" s="20">
+      <c r="G90" s="22">
         <v>52.613</v>
       </c>
-      <c r="H90" s="21">
+      <c r="H90" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="20">
+      <c r="A91" s="22">
         <v>46.228000000000002</v>
       </c>
-      <c r="B91" s="20">
+      <c r="B91" s="22">
         <v>11.183999999999999</v>
       </c>
-      <c r="C91" s="20">
+      <c r="C91" s="22">
         <v>42.308</v>
       </c>
-      <c r="D91" s="20">
+      <c r="D91" s="22">
         <v>50.148000000000003</v>
       </c>
-      <c r="E91" s="21">
-        <v>1</v>
-      </c>
-      <c r="F91" s="20">
+      <c r="E91" s="23">
+        <v>1</v>
+      </c>
+      <c r="F91" s="22">
         <v>41.612000000000002</v>
       </c>
-      <c r="G91" s="20">
+      <c r="G91" s="22">
         <v>50.844000000000001</v>
       </c>
-      <c r="H91" s="21">
+      <c r="H91" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="20">
+      <c r="A92" s="22">
         <v>47.128999999999998</v>
       </c>
-      <c r="B92" s="20">
+      <c r="B92" s="22">
         <v>11.661</v>
       </c>
-      <c r="C92" s="20">
+      <c r="C92" s="22">
         <v>43.209000000000003</v>
       </c>
-      <c r="D92" s="20">
+      <c r="D92" s="22">
         <v>51.048999999999999</v>
       </c>
-      <c r="E92" s="21">
-        <v>1</v>
-      </c>
-      <c r="F92" s="20">
+      <c r="E92" s="23">
+        <v>1</v>
+      </c>
+      <c r="F92" s="22">
         <v>42.316000000000003</v>
       </c>
-      <c r="G92" s="20">
+      <c r="G92" s="22">
         <v>51.942999999999998</v>
       </c>
-      <c r="H92" s="21">
+      <c r="H92" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="20">
+      <c r="A93" s="22">
         <v>45.956000000000003</v>
       </c>
-      <c r="B93" s="20">
+      <c r="B93" s="22">
         <v>7.3460000000000001</v>
       </c>
-      <c r="C93" s="20">
+      <c r="C93" s="22">
         <v>42.036999999999999</v>
       </c>
-      <c r="D93" s="20">
+      <c r="D93" s="22">
         <v>49.875999999999998</v>
       </c>
-      <c r="E93" s="21">
-        <v>1</v>
-      </c>
-      <c r="F93" s="20">
+      <c r="E93" s="23">
+        <v>1</v>
+      </c>
+      <c r="F93" s="22">
         <v>42.923999999999999</v>
       </c>
-      <c r="G93" s="20">
+      <c r="G93" s="22">
         <v>48.988999999999997</v>
       </c>
-      <c r="H93" s="21">
+      <c r="H93" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="20">
+      <c r="A94" s="22">
         <v>48.415999999999997</v>
       </c>
-      <c r="B94" s="20">
+      <c r="B94" s="22">
         <v>10.394</v>
       </c>
-      <c r="C94" s="20">
+      <c r="C94" s="22">
         <v>44.496000000000002</v>
       </c>
-      <c r="D94" s="20">
+      <c r="D94" s="22">
         <v>52.335000000000001</v>
       </c>
-      <c r="E94" s="21">
-        <v>1</v>
-      </c>
-      <c r="F94" s="20">
+      <c r="E94" s="23">
+        <v>1</v>
+      </c>
+      <c r="F94" s="22">
         <v>44.125</v>
       </c>
-      <c r="G94" s="20">
+      <c r="G94" s="22">
         <v>52.706000000000003</v>
       </c>
-      <c r="H94" s="21">
+      <c r="H94" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="20">
+      <c r="A95" s="22">
         <v>45.728999999999999</v>
       </c>
-      <c r="B95" s="20">
+      <c r="B95" s="22">
         <v>9.6229999999999993</v>
       </c>
-      <c r="C95" s="20">
+      <c r="C95" s="22">
         <v>41.808999999999997</v>
       </c>
-      <c r="D95" s="20">
+      <c r="D95" s="22">
         <v>49.649000000000001</v>
       </c>
-      <c r="E95" s="21">
-        <v>1</v>
-      </c>
-      <c r="F95" s="20">
+      <c r="E95" s="23">
+        <v>1</v>
+      </c>
+      <c r="F95" s="22">
         <v>41.756999999999998</v>
       </c>
-      <c r="G95" s="20">
+      <c r="G95" s="22">
         <v>49.701000000000001</v>
       </c>
-      <c r="H95" s="21">
+      <c r="H95" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="20">
+      <c r="A96" s="22">
         <v>46.258000000000003</v>
       </c>
-      <c r="B96" s="20">
+      <c r="B96" s="22">
         <v>8.1880000000000006</v>
       </c>
-      <c r="C96" s="20">
+      <c r="C96" s="22">
         <v>42.338000000000001</v>
       </c>
-      <c r="D96" s="20">
+      <c r="D96" s="22">
         <v>50.177999999999997</v>
       </c>
-      <c r="E96" s="21">
-        <v>1</v>
-      </c>
-      <c r="F96" s="20">
+      <c r="E96" s="23">
+        <v>1</v>
+      </c>
+      <c r="F96" s="22">
         <v>42.878</v>
       </c>
-      <c r="G96" s="20">
+      <c r="G96" s="22">
         <v>49.637</v>
       </c>
-      <c r="H96" s="21">
+      <c r="H96" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="20">
+      <c r="A97" s="22">
         <v>47.731000000000002</v>
       </c>
-      <c r="B97" s="20">
+      <c r="B97" s="22">
         <v>10.079000000000001</v>
       </c>
-      <c r="C97" s="20">
+      <c r="C97" s="22">
         <v>43.811</v>
       </c>
-      <c r="D97" s="20">
+      <c r="D97" s="22">
         <v>51.651000000000003</v>
       </c>
-      <c r="E97" s="21">
-        <v>1</v>
-      </c>
-      <c r="F97" s="20">
+      <c r="E97" s="23">
+        <v>1</v>
+      </c>
+      <c r="F97" s="22">
         <v>43.57</v>
       </c>
-      <c r="G97" s="20">
+      <c r="G97" s="22">
         <v>51.892000000000003</v>
       </c>
-      <c r="H97" s="21">
+      <c r="H97" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="20">
+      <c r="A98" s="22">
         <v>43.140999999999998</v>
       </c>
-      <c r="B98" s="20">
+      <c r="B98" s="22">
         <v>10.478999999999999</v>
       </c>
-      <c r="C98" s="20">
+      <c r="C98" s="22">
         <v>39.220999999999997</v>
       </c>
-      <c r="D98" s="20">
+      <c r="D98" s="22">
         <v>47.061</v>
       </c>
-      <c r="E98" s="21">
-        <v>1</v>
-      </c>
-      <c r="F98" s="20">
+      <c r="E98" s="23">
+        <v>1</v>
+      </c>
+      <c r="F98" s="22">
         <v>38.816000000000003</v>
       </c>
-      <c r="G98" s="20">
+      <c r="G98" s="22">
         <v>47.466000000000001</v>
       </c>
-      <c r="H98" s="21">
+      <c r="H98" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="20">
+      <c r="A99" s="22">
         <v>46.982999999999997</v>
       </c>
-      <c r="B99" s="20">
+      <c r="B99" s="22">
         <v>9.3889999999999993</v>
       </c>
-      <c r="C99" s="20">
+      <c r="C99" s="22">
         <v>43.063000000000002</v>
       </c>
-      <c r="D99" s="20">
+      <c r="D99" s="22">
         <v>50.902000000000001</v>
       </c>
-      <c r="E99" s="21">
-        <v>1</v>
-      </c>
-      <c r="F99" s="20">
+      <c r="E99" s="23">
+        <v>1</v>
+      </c>
+      <c r="F99" s="22">
         <v>43.106999999999999</v>
       </c>
-      <c r="G99" s="20">
+      <c r="G99" s="22">
         <v>50.857999999999997</v>
       </c>
-      <c r="H99" s="21">
+      <c r="H99" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="20">
+      <c r="A100" s="22">
         <v>42.030999999999999</v>
       </c>
-      <c r="B100" s="20">
+      <c r="B100" s="22">
         <v>9.5660000000000007</v>
       </c>
-      <c r="C100" s="20">
+      <c r="C100" s="22">
         <v>38.110999999999997</v>
       </c>
-      <c r="D100" s="20">
+      <c r="D100" s="22">
         <v>45.951000000000001</v>
       </c>
-      <c r="E100" s="21">
+      <c r="E100" s="23">
         <v>0</v>
       </c>
-      <c r="F100" s="20">
+      <c r="F100" s="22">
         <v>38.082000000000001</v>
       </c>
-      <c r="G100" s="20">
+      <c r="G100" s="22">
         <v>45.98</v>
       </c>
-      <c r="H100" s="21">
+      <c r="H100" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="20">
+      <c r="A101" s="22">
         <v>45.466999999999999</v>
       </c>
-      <c r="B101" s="20">
+      <c r="B101" s="22">
         <v>9.4120000000000008</v>
       </c>
-      <c r="C101" s="20">
+      <c r="C101" s="22">
         <v>41.546999999999997</v>
       </c>
-      <c r="D101" s="20">
+      <c r="D101" s="22">
         <v>49.387</v>
       </c>
-      <c r="E101" s="21">
-        <v>1</v>
-      </c>
-      <c r="F101" s="20">
+      <c r="E101" s="23">
+        <v>1</v>
+      </c>
+      <c r="F101" s="22">
         <v>41.582000000000001</v>
       </c>
-      <c r="G101" s="20">
+      <c r="G101" s="22">
         <v>49.351999999999997</v>
       </c>
-      <c r="H101" s="21">
+      <c r="H101" s="23">
         <v>1</v>
       </c>
     </row>

--- a/data/kapitola_07.xlsx
+++ b/data/kapitola_07.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA5AAECC-8540-486B-ADF6-E18993572D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16AD2844-C4D1-43D1-9D19-41E5A7868515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{7F358E05-1A53-46D8-959C-57B782BAF302}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{6742615C-8610-4DDA-A7C8-6B97C5BB6E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Prehled" sheetId="1" r:id="rId1"/>
@@ -598,9 +598,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="[&lt;0.001]&quot;&lt; 0,001&quot;;0.0000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -680,7 +681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -719,6 +720,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1084,7 +1088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7F8500-873D-4111-A43D-A7560B988938}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB9C8FE1-ABE9-408B-AC42-062BE530BD74}">
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1093,11 +1097,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
     </row>
     <row r="2" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1105,32 +1109,32 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
     </row>
     <row r="4" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
     </row>
     <row r="5" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
     </row>
     <row r="6" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
     </row>
     <row r="7" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -1369,7 +1373,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E78151DA-05CF-4295-836B-8472D8744DD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E2F939-5A42-41E0-98D9-F4F6A6441D4B}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1385,49 +1389,49 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>15</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>36</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>104.5</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1439,7 +1443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43D5EA3-54C0-4616-8A33-217BE3986ADF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{500D8333-6629-42C3-B3F4-9059BB3D3757}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1455,49 +1459,49 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>10</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>25</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>100</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1509,7 +1513,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E4DCC78-F99F-4F08-8FDC-6C50E0DF4EC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0231346-74A3-43B0-892B-97FC252E2A54}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1521,67 +1525,67 @@
       <c r="A1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="16">
         <v>12</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="16">
         <v>15</v>
       </c>
-      <c r="C3" s="17"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="16">
         <v>9</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>14</v>
       </c>
-      <c r="C5" s="17"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <v>11</v>
       </c>
-      <c r="C6" s="17"/>
+      <c r="C6" s="18"/>
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="16">
         <v>13</v>
       </c>
-      <c r="C7" s="17"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="16">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="16">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="16">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="16">
         <v>14</v>
       </c>
     </row>
@@ -1595,7 +1599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA25C09A-9B5A-4908-9694-E728E0F2AA74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE89DB32-3945-4031-A44F-6C05CC4ABA84}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1611,55 +1615,55 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>30</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>16</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>32.4</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>4.8</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1671,7 +1675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E74FA6-DB2B-4AB1-AB0B-BF58C5283F79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E9098B5-A1CB-41FA-A126-E171BF8D21D4}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1683,117 +1687,117 @@
       <c r="A1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="16">
         <v>18</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="16">
         <v>22</v>
       </c>
-      <c r="C3" s="17"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="16">
         <v>25</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <v>24</v>
       </c>
-      <c r="C6" s="17"/>
+      <c r="C6" s="18"/>
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="16">
         <v>21</v>
       </c>
-      <c r="C7" s="17"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="16">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="16">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="16">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="16">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="16">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="16">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="16">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="16">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="16">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="16">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="16">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="16">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="16">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="16">
         <v>22</v>
       </c>
     </row>
@@ -1807,7 +1811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A66FFD-F61E-458C-9D41-B6108700D87E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10B7FB7-32B6-4454-B159-5DD4CCE4F53A}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1828,91 +1832,91 @@
       <c r="D1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="16">
         <v>480</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="16">
         <v>495</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="19" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="16">
         <v>490</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="16">
         <v>515</v>
       </c>
-      <c r="F3" s="17"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="16">
         <v>500</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="16">
         <v>520</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <v>505</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>540</v>
       </c>
-      <c r="F5" s="17"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <v>492</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <v>498</v>
       </c>
-      <c r="F6" s="17"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F7" s="17"/>
+      <c r="F7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1924,7 +1928,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5802A304-B50D-4D72-9DE7-6A12956BA0F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4E0DEF-46B5-4514-9D8F-99BA3EB90F71}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1940,55 +1944,55 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>15</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>6</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>25</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>2</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2000,7 +2004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB4CDC6-614A-49C1-919D-45FB35EE737C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1D539A-97F6-4DD1-BF90-8774E23F782D}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2016,61 +2020,61 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>25</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>2</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>25.6</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>6</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>150</v>
       </c>
-      <c r="D6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2082,7 +2086,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF74184-A6B4-41A5-A9FB-B6D772D306B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04DCFD0F-4C52-424B-BBF2-1F5EDFEC869F}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2106,106 +2110,106 @@
       <c r="E1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>473.6</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="16">
         <v>511.4</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="16">
         <v>476.6</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="16">
         <v>508.4</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="19" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>503</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="16">
         <v>512</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="16">
         <v>503.7</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="16">
         <v>511.3</v>
       </c>
-      <c r="G3" s="17"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>488</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="16">
         <v>506</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="16">
         <v>489.4</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="16">
         <v>504.6</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>525</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <v>560</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>527.79999999999995</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <v>557.20000000000005</v>
       </c>
-      <c r="G5" s="17"/>
+      <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>505</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <v>535</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <v>507.4</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="16">
         <v>532.6</v>
       </c>
-      <c r="G6" s="17"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G7" s="17"/>
+      <c r="G7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2217,7 +2221,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDCDED2D-5F16-43DF-B620-CFEE5252AB68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B55979-059F-4BF0-85B8-BFABEF510561}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2233,61 +2237,61 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>50</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>3</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>48.2</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>10</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>200</v>
       </c>
-      <c r="D6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2299,7 +2303,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3702512B-573B-42EF-8BA6-2A9B53B380D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17CC3A7-0459-427D-BD61-4A2A9ED93224}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2336,7 +2340,7 @@
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="5">
@@ -2581,7 +2585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4CC5FC-7F36-444F-A54A-8D2E46AD4BE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1419F6-39A1-4442-8409-67783F8C20BE}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2865,7 +2869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4D95A8-2A06-412C-AF7D-139627EF1BDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F679A6C-AD6B-4C81-856F-76D599EEADD2}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3158,7 +3162,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFABC76-7C1A-49FD-A164-638E6BD096D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6B8542-C228-4BBD-A016-12AA7429441B}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3482,7 +3486,7 @@
       <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="14">
         <f>_xlfn.T.DIST(B24,B10,TRUE)</f>
         <v>4.6538715043555148E-18</v>
       </c>
@@ -3512,7 +3516,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D47865-12D1-4EAF-B618-D59A150A4484}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7017D061-7BFD-4995-A04E-2376CD44E840}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3528,73 +3532,73 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>50</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>10</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>25</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>46</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>10</v>
       </c>
-      <c r="D6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="16">
         <v>0.95</v>
       </c>
-      <c r="D7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
     <row r="8" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="16">
         <v>0.05</v>
       </c>
     </row>
@@ -3608,7 +3612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37BC2E3-EC13-46F7-908D-7403BAB346B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BE0351-998C-41C5-8A59-A256D37D1E21}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3624,55 +3628,55 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>100</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>56</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>104.125</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>12.584</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3684,7 +3688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD6727E8-A514-4123-99C3-0C0C20FF0199}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F983BD30-62D1-4248-B2D7-1275C83F5098}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3705,91 +3709,91 @@
       <c r="D1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>46</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="16">
         <v>10</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="16">
         <v>25</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="19" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="16">
         <v>48.5</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="16">
         <v>10</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="16">
         <v>400</v>
       </c>
-      <c r="F3" s="17"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>50.4</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="16">
         <v>10</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="16">
         <v>400</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>44</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <v>10</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>100</v>
       </c>
-      <c r="F5" s="17"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>47</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <v>10</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <v>100</v>
       </c>
-      <c r="F6" s="17"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F7" s="17"/>
+      <c r="F7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3801,7 +3805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CAB5280-C020-4E30-8719-1FF1ECD4670C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC07B69-E8FB-4031-B58D-6B9AA866EB70}">
   <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3834,2617 +3838,2617 @@
       <c r="H1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22">
+      <c r="A2" s="23">
         <v>48.058999999999997</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="23">
         <v>10.952</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="23">
         <v>44.14</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="23">
         <v>51.978999999999999</v>
       </c>
-      <c r="E2" s="23">
-        <v>1</v>
-      </c>
-      <c r="F2" s="22">
+      <c r="E2" s="24">
+        <v>1</v>
+      </c>
+      <c r="F2" s="23">
         <v>43.539000000000001</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="23">
         <v>52.58</v>
       </c>
-      <c r="H2" s="23">
-        <v>1</v>
-      </c>
-      <c r="J2" s="18" t="s">
+      <c r="H2" s="24">
+        <v>1</v>
+      </c>
+      <c r="J2" s="19" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
+      <c r="A3" s="23">
         <v>44.823</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="23">
         <v>10.125</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="23">
         <v>40.902999999999999</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="23">
         <v>48.743000000000002</v>
       </c>
-      <c r="E3" s="23">
-        <v>1</v>
-      </c>
-      <c r="F3" s="22">
+      <c r="E3" s="24">
+        <v>1</v>
+      </c>
+      <c r="F3" s="23">
         <v>40.643000000000001</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="23">
         <v>49.002000000000002</v>
       </c>
-      <c r="H3" s="23">
-        <v>1</v>
-      </c>
-      <c r="J3" s="17"/>
+      <c r="H3" s="24">
+        <v>1</v>
+      </c>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+      <c r="A4" s="23">
         <v>46.776000000000003</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="23">
         <v>6.7850000000000001</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="23">
         <v>42.856000000000002</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="23">
         <v>50.695999999999998</v>
       </c>
-      <c r="E4" s="23">
-        <v>1</v>
-      </c>
-      <c r="F4" s="22">
+      <c r="E4" s="24">
+        <v>1</v>
+      </c>
+      <c r="F4" s="23">
         <v>43.975000000000001</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="23">
         <v>49.576999999999998</v>
       </c>
-      <c r="H4" s="23">
-        <v>1</v>
-      </c>
-      <c r="J4" s="18" t="s">
+      <c r="H4" s="24">
+        <v>1</v>
+      </c>
+      <c r="J4" s="19" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+      <c r="A5" s="23">
         <v>44.707999999999998</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="23">
         <v>8.3079999999999998</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="23">
         <v>40.787999999999997</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="23">
         <v>48.628</v>
       </c>
-      <c r="E5" s="23">
-        <v>1</v>
-      </c>
-      <c r="F5" s="22">
+      <c r="E5" s="24">
+        <v>1</v>
+      </c>
+      <c r="F5" s="23">
         <v>41.277999999999999</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="23">
         <v>48.137</v>
       </c>
-      <c r="H5" s="23">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17"/>
+      <c r="H5" s="24">
+        <v>1</v>
+      </c>
+      <c r="J5" s="18"/>
     </row>
     <row r="6" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
+      <c r="A6" s="23">
         <v>45.088999999999999</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="23">
         <v>8.8420000000000005</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <v>41.168999999999997</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="23">
         <v>49.009</v>
       </c>
-      <c r="E6" s="23">
-        <v>1</v>
-      </c>
-      <c r="F6" s="22">
+      <c r="E6" s="24">
+        <v>1</v>
+      </c>
+      <c r="F6" s="23">
         <v>41.439</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="23">
         <v>48.738999999999997</v>
       </c>
-      <c r="H6" s="23">
-        <v>1</v>
-      </c>
-      <c r="J6" s="17"/>
+      <c r="H6" s="24">
+        <v>1</v>
+      </c>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="23">
         <v>45.948999999999998</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="23">
         <v>7.9770000000000003</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="23">
         <v>42.029000000000003</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <v>49.869</v>
       </c>
-      <c r="E7" s="23">
-        <v>1</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="E7" s="24">
+        <v>1</v>
+      </c>
+      <c r="F7" s="23">
         <v>42.655999999999999</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <v>49.241999999999997</v>
       </c>
-      <c r="H7" s="23">
-        <v>1</v>
-      </c>
-      <c r="J7" s="17"/>
+      <c r="H7" s="24">
+        <v>1</v>
+      </c>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+      <c r="A8" s="23">
         <v>45.710999999999999</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="23">
         <v>9.7110000000000003</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <v>41.790999999999997</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <v>49.631</v>
       </c>
-      <c r="E8" s="23">
-        <v>1</v>
-      </c>
-      <c r="F8" s="22">
+      <c r="E8" s="24">
+        <v>1</v>
+      </c>
+      <c r="F8" s="23">
         <v>41.701999999999998</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <v>49.719000000000001</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+      <c r="A9" s="23">
         <v>47.033000000000001</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="23">
         <v>11.488</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <v>43.113</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="23">
         <v>50.953000000000003</v>
       </c>
-      <c r="E9" s="23">
-        <v>1</v>
-      </c>
-      <c r="F9" s="22">
+      <c r="E9" s="24">
+        <v>1</v>
+      </c>
+      <c r="F9" s="23">
         <v>42.290999999999997</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="23">
         <v>51.774999999999999</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+      <c r="A10" s="23">
         <v>43.753</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="23">
         <v>8.61</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <v>39.832999999999998</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <v>47.673000000000002</v>
       </c>
-      <c r="E10" s="23">
-        <v>1</v>
-      </c>
-      <c r="F10" s="22">
+      <c r="E10" s="24">
+        <v>1</v>
+      </c>
+      <c r="F10" s="23">
         <v>40.198999999999998</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="23">
         <v>47.307000000000002</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+      <c r="A11" s="23">
         <v>50.189</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="23">
         <v>9.3789999999999996</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <v>46.27</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <v>54.109000000000002</v>
       </c>
-      <c r="E11" s="23">
-        <v>1</v>
-      </c>
-      <c r="F11" s="22">
+      <c r="E11" s="24">
+        <v>1</v>
+      </c>
+      <c r="F11" s="23">
         <v>46.317999999999998</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <v>54.061</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+      <c r="A12" s="23">
         <v>49.22</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="23">
         <v>8.2650000000000006</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="23">
         <v>45.3</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="23">
         <v>53.14</v>
       </c>
-      <c r="E12" s="23">
-        <v>1</v>
-      </c>
-      <c r="F12" s="22">
+      <c r="E12" s="24">
+        <v>1</v>
+      </c>
+      <c r="F12" s="23">
         <v>45.808</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="23">
         <v>52.631</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
+      <c r="A13" s="23">
         <v>49.326999999999998</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="23">
         <v>9.4359999999999999</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="23">
         <v>45.406999999999996</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="23">
         <v>53.247</v>
       </c>
-      <c r="E13" s="23">
-        <v>1</v>
-      </c>
-      <c r="F13" s="22">
+      <c r="E13" s="24">
+        <v>1</v>
+      </c>
+      <c r="F13" s="23">
         <v>45.432000000000002</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="23">
         <v>53.222000000000001</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="23">
         <v>44.134</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="23">
         <v>7.6269999999999998</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="23">
         <v>40.213999999999999</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="23">
         <v>48.054000000000002</v>
       </c>
-      <c r="E14" s="23">
-        <v>1</v>
-      </c>
-      <c r="F14" s="22">
+      <c r="E14" s="24">
+        <v>1</v>
+      </c>
+      <c r="F14" s="23">
         <v>40.985999999999997</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <v>47.281999999999996</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+      <c r="A15" s="23">
         <v>46.744</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="23">
         <v>10.616</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="23">
         <v>42.823999999999998</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="23">
         <v>50.664000000000001</v>
       </c>
-      <c r="E15" s="23">
-        <v>1</v>
-      </c>
-      <c r="F15" s="22">
+      <c r="E15" s="24">
+        <v>1</v>
+      </c>
+      <c r="F15" s="23">
         <v>42.360999999999997</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <v>51.125999999999998</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+      <c r="A16" s="23">
         <v>43.478999999999999</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="23">
         <v>9.6159999999999997</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="23">
         <v>39.558999999999997</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="23">
         <v>47.399000000000001</v>
       </c>
-      <c r="E16" s="23">
-        <v>1</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="E16" s="24">
+        <v>1</v>
+      </c>
+      <c r="F16" s="23">
         <v>39.509</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>47.448</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+      <c r="A17" s="23">
         <v>45.753999999999998</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="23">
         <v>11.154999999999999</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="23">
         <v>41.834000000000003</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <v>49.673999999999999</v>
       </c>
-      <c r="E17" s="23">
-        <v>1</v>
-      </c>
-      <c r="F17" s="22">
+      <c r="E17" s="24">
+        <v>1</v>
+      </c>
+      <c r="F17" s="23">
         <v>41.149000000000001</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <v>50.357999999999997</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22">
+      <c r="A18" s="23">
         <v>45.808999999999997</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="23">
         <v>9.8130000000000006</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="23">
         <v>41.889000000000003</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="23">
         <v>49.728999999999999</v>
       </c>
-      <c r="E18" s="23">
-        <v>1</v>
-      </c>
-      <c r="F18" s="22">
+      <c r="E18" s="24">
+        <v>1</v>
+      </c>
+      <c r="F18" s="23">
         <v>41.758000000000003</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="23">
         <v>49.859000000000002</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="22">
+      <c r="A19" s="23">
         <v>49.216999999999999</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="23">
         <v>10.031000000000001</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="23">
         <v>45.296999999999997</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <v>53.137</v>
       </c>
-      <c r="E19" s="23">
-        <v>1</v>
-      </c>
-      <c r="F19" s="22">
+      <c r="E19" s="24">
+        <v>1</v>
+      </c>
+      <c r="F19" s="23">
         <v>45.076000000000001</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="23">
         <v>53.356999999999999</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22">
+      <c r="A20" s="23">
         <v>46.570999999999998</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="23">
         <v>9.8109999999999999</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <v>42.651000000000003</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <v>50.491</v>
       </c>
-      <c r="E20" s="23">
-        <v>1</v>
-      </c>
-      <c r="F20" s="22">
+      <c r="E20" s="24">
+        <v>1</v>
+      </c>
+      <c r="F20" s="23">
         <v>42.521999999999998</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="23">
         <v>50.621000000000002</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22">
+      <c r="A21" s="23">
         <v>42.893999999999998</v>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="23">
         <v>11.667</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="23">
         <v>38.973999999999997</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <v>46.814</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <v>0</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="23">
         <v>38.079000000000001</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="23">
         <v>47.71</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22">
+      <c r="A22" s="23">
         <v>51.426000000000002</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="23">
         <v>10.516</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="23">
         <v>47.506</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <v>55.345999999999997</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <v>0</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="23">
         <v>47.085000000000001</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="23">
         <v>55.765999999999998</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22">
+      <c r="A23" s="23">
         <v>42.328000000000003</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="23">
         <v>12.051</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="23">
         <v>38.408000000000001</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <v>46.247999999999998</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>0</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="23">
         <v>37.353999999999999</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="23">
         <v>47.302999999999997</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="22">
+      <c r="A24" s="23">
         <v>48.484000000000002</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="23">
         <v>13.532</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <v>44.564</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <v>52.404000000000003</v>
       </c>
-      <c r="E24" s="23">
-        <v>1</v>
-      </c>
-      <c r="F24" s="22">
+      <c r="E24" s="24">
+        <v>1</v>
+      </c>
+      <c r="F24" s="23">
         <v>42.898000000000003</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="23">
         <v>54.07</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22">
+      <c r="A25" s="23">
         <v>49.048999999999999</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="23">
         <v>10.119</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <v>45.128999999999998</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <v>52.969000000000001</v>
       </c>
-      <c r="E25" s="23">
-        <v>1</v>
-      </c>
-      <c r="F25" s="22">
+      <c r="E25" s="24">
+        <v>1</v>
+      </c>
+      <c r="F25" s="23">
         <v>44.872</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="23">
         <v>53.225999999999999</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22">
+      <c r="A26" s="23">
         <v>46.911000000000001</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="23">
         <v>12.042</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="23">
         <v>42.991</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="23">
         <v>50.831000000000003</v>
       </c>
-      <c r="E26" s="23">
-        <v>1</v>
-      </c>
-      <c r="F26" s="22">
+      <c r="E26" s="24">
+        <v>1</v>
+      </c>
+      <c r="F26" s="23">
         <v>41.941000000000003</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="23">
         <v>51.881999999999998</v>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="22">
+      <c r="A27" s="23">
         <v>46.603000000000002</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="23">
         <v>10.358000000000001</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="23">
         <v>42.683</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="23">
         <v>50.523000000000003</v>
       </c>
-      <c r="E27" s="23">
-        <v>1</v>
-      </c>
-      <c r="F27" s="22">
+      <c r="E27" s="24">
+        <v>1</v>
+      </c>
+      <c r="F27" s="23">
         <v>42.328000000000003</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="23">
         <v>50.878999999999998</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="22">
+      <c r="A28" s="23">
         <v>49.093000000000004</v>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="23">
         <v>7.35</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="23">
         <v>45.173000000000002</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="23">
         <v>53.012999999999998</v>
       </c>
-      <c r="E28" s="23">
-        <v>1</v>
-      </c>
-      <c r="F28" s="22">
+      <c r="E28" s="24">
+        <v>1</v>
+      </c>
+      <c r="F28" s="23">
         <v>46.058999999999997</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="23">
         <v>52.127000000000002</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22">
+      <c r="A29" s="23">
         <v>46.316000000000003</v>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="23">
         <v>10.512</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="23">
         <v>42.396000000000001</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="23">
         <v>50.234999999999999</v>
       </c>
-      <c r="E29" s="23">
-        <v>1</v>
-      </c>
-      <c r="F29" s="22">
+      <c r="E29" s="24">
+        <v>1</v>
+      </c>
+      <c r="F29" s="23">
         <v>41.976999999999997</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="23">
         <v>50.655000000000001</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22">
+      <c r="A30" s="23">
         <v>47.067</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="23">
         <v>14.547000000000001</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="23">
         <v>43.148000000000003</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="23">
         <v>50.987000000000002</v>
       </c>
-      <c r="E30" s="23">
-        <v>1</v>
-      </c>
-      <c r="F30" s="22">
+      <c r="E30" s="24">
+        <v>1</v>
+      </c>
+      <c r="F30" s="23">
         <v>41.063000000000002</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="23">
         <v>53.072000000000003</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="22">
+      <c r="A31" s="23">
         <v>44.073</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="23">
         <v>8.6869999999999994</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <v>40.152999999999999</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <v>47.991999999999997</v>
       </c>
-      <c r="E31" s="23">
-        <v>1</v>
-      </c>
-      <c r="F31" s="22">
+      <c r="E31" s="24">
+        <v>1</v>
+      </c>
+      <c r="F31" s="23">
         <v>40.485999999999997</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="23">
         <v>47.658999999999999</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22">
+      <c r="A32" s="23">
         <v>46.811999999999998</v>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <v>7.5810000000000004</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="23">
         <v>42.892000000000003</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="23">
         <v>50.731999999999999</v>
       </c>
-      <c r="E32" s="23">
-        <v>1</v>
-      </c>
-      <c r="F32" s="22">
+      <c r="E32" s="24">
+        <v>1</v>
+      </c>
+      <c r="F32" s="23">
         <v>43.683</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="23">
         <v>49.942</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="22">
+      <c r="A33" s="23">
         <v>46.722999999999999</v>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="23">
         <v>9.3010000000000002</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="23">
         <v>42.802999999999997</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="23">
         <v>50.643000000000001</v>
       </c>
-      <c r="E33" s="23">
-        <v>1</v>
-      </c>
-      <c r="F33" s="22">
+      <c r="E33" s="24">
+        <v>1</v>
+      </c>
+      <c r="F33" s="23">
         <v>42.883000000000003</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="23">
         <v>50.561999999999998</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="22">
+      <c r="A34" s="23">
         <v>47.588999999999999</v>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="23">
         <v>10.27</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="23">
         <v>43.67</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="23">
         <v>51.509</v>
       </c>
-      <c r="E34" s="23">
-        <v>1</v>
-      </c>
-      <c r="F34" s="22">
+      <c r="E34" s="24">
+        <v>1</v>
+      </c>
+      <c r="F34" s="23">
         <v>43.35</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="23">
         <v>51.829000000000001</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="22">
+      <c r="A35" s="23">
         <v>47.636000000000003</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="23">
         <v>9.1300000000000008</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="23">
         <v>43.716000000000001</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="23">
         <v>51.555</v>
       </c>
-      <c r="E35" s="23">
-        <v>1</v>
-      </c>
-      <c r="F35" s="22">
+      <c r="E35" s="24">
+        <v>1</v>
+      </c>
+      <c r="F35" s="23">
         <v>43.866999999999997</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="23">
         <v>51.404000000000003</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="22">
+      <c r="A36" s="23">
         <v>48.197000000000003</v>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="23">
         <v>8.0890000000000004</v>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="23">
         <v>44.277000000000001</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="23">
         <v>52.116999999999997</v>
       </c>
-      <c r="E36" s="23">
-        <v>1</v>
-      </c>
-      <c r="F36" s="22">
+      <c r="E36" s="24">
+        <v>1</v>
+      </c>
+      <c r="F36" s="23">
         <v>44.857999999999997</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="23">
         <v>51.536000000000001</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="22">
+      <c r="A37" s="23">
         <v>48.54</v>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="23">
         <v>8.077</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="23">
         <v>44.62</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="23">
         <v>52.46</v>
       </c>
-      <c r="E37" s="23">
-        <v>1</v>
-      </c>
-      <c r="F37" s="22">
+      <c r="E37" s="24">
+        <v>1</v>
+      </c>
+      <c r="F37" s="23">
         <v>45.206000000000003</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G37" s="23">
         <v>51.874000000000002</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="22">
+      <c r="A38" s="23">
         <v>46.853999999999999</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="23">
         <v>7.6710000000000003</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="23">
         <v>42.933999999999997</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="23">
         <v>50.774000000000001</v>
       </c>
-      <c r="E38" s="23">
-        <v>1</v>
-      </c>
-      <c r="F38" s="22">
+      <c r="E38" s="24">
+        <v>1</v>
+      </c>
+      <c r="F38" s="23">
         <v>43.688000000000002</v>
       </c>
-      <c r="G38" s="22">
+      <c r="G38" s="23">
         <v>50.021000000000001</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="22">
+      <c r="A39" s="23">
         <v>44.548999999999999</v>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="23">
         <v>8.8940000000000001</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="23">
         <v>40.628999999999998</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="23">
         <v>48.469000000000001</v>
       </c>
-      <c r="E39" s="23">
-        <v>1</v>
-      </c>
-      <c r="F39" s="22">
+      <c r="E39" s="24">
+        <v>1</v>
+      </c>
+      <c r="F39" s="23">
         <v>40.878</v>
       </c>
-      <c r="G39" s="22">
+      <c r="G39" s="23">
         <v>48.220999999999997</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="22">
+      <c r="A40" s="23">
         <v>46.652999999999999</v>
       </c>
-      <c r="B40" s="22">
+      <c r="B40" s="23">
         <v>9.5570000000000004</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="23">
         <v>42.734000000000002</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="23">
         <v>50.573</v>
       </c>
-      <c r="E40" s="23">
-        <v>1</v>
-      </c>
-      <c r="F40" s="22">
+      <c r="E40" s="24">
+        <v>1</v>
+      </c>
+      <c r="F40" s="23">
         <v>42.707999999999998</v>
       </c>
-      <c r="G40" s="22">
+      <c r="G40" s="23">
         <v>50.598999999999997</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="22">
+      <c r="A41" s="23">
         <v>47.59</v>
       </c>
-      <c r="B41" s="22">
+      <c r="B41" s="23">
         <v>10.672000000000001</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="23">
         <v>43.67</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="23">
         <v>51.51</v>
       </c>
-      <c r="E41" s="23">
-        <v>1</v>
-      </c>
-      <c r="F41" s="22">
+      <c r="E41" s="24">
+        <v>1</v>
+      </c>
+      <c r="F41" s="23">
         <v>43.185000000000002</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="23">
         <v>51.994999999999997</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="22">
+      <c r="A42" s="23">
         <v>48.357999999999997</v>
       </c>
-      <c r="B42" s="22">
+      <c r="B42" s="23">
         <v>9.6059999999999999</v>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="23">
         <v>44.438000000000002</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="23">
         <v>52.277999999999999</v>
       </c>
-      <c r="E42" s="23">
-        <v>1</v>
-      </c>
-      <c r="F42" s="22">
+      <c r="E42" s="24">
+        <v>1</v>
+      </c>
+      <c r="F42" s="23">
         <v>44.393000000000001</v>
       </c>
-      <c r="G42" s="22">
+      <c r="G42" s="23">
         <v>52.323999999999998</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="22">
+      <c r="A43" s="23">
         <v>49.445999999999998</v>
       </c>
-      <c r="B43" s="22">
+      <c r="B43" s="23">
         <v>12.071</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="23">
         <v>45.526000000000003</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="23">
         <v>53.366</v>
       </c>
-      <c r="E43" s="23">
-        <v>1</v>
-      </c>
-      <c r="F43" s="22">
+      <c r="E43" s="24">
+        <v>1</v>
+      </c>
+      <c r="F43" s="23">
         <v>44.463999999999999</v>
       </c>
-      <c r="G43" s="22">
+      <c r="G43" s="23">
         <v>54.429000000000002</v>
       </c>
-      <c r="H43" s="23">
+      <c r="H43" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="22">
+      <c r="A44" s="23">
         <v>47.527999999999999</v>
       </c>
-      <c r="B44" s="22">
+      <c r="B44" s="23">
         <v>9.7479999999999993</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="23">
         <v>43.607999999999997</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="23">
         <v>51.448</v>
       </c>
-      <c r="E44" s="23">
-        <v>1</v>
-      </c>
-      <c r="F44" s="22">
+      <c r="E44" s="24">
+        <v>1</v>
+      </c>
+      <c r="F44" s="23">
         <v>43.503999999999998</v>
       </c>
-      <c r="G44" s="22">
+      <c r="G44" s="23">
         <v>51.552</v>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="22">
+      <c r="A45" s="23">
         <v>46.244</v>
       </c>
-      <c r="B45" s="22">
+      <c r="B45" s="23">
         <v>7.3970000000000002</v>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="23">
         <v>42.323999999999998</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="23">
         <v>50.164000000000001</v>
       </c>
-      <c r="E45" s="23">
-        <v>1</v>
-      </c>
-      <c r="F45" s="22">
+      <c r="E45" s="24">
+        <v>1</v>
+      </c>
+      <c r="F45" s="23">
         <v>43.191000000000003</v>
       </c>
-      <c r="G45" s="22">
+      <c r="G45" s="23">
         <v>49.296999999999997</v>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="22">
+      <c r="A46" s="23">
         <v>48.274999999999999</v>
       </c>
-      <c r="B46" s="22">
+      <c r="B46" s="23">
         <v>9.2050000000000001</v>
       </c>
-      <c r="C46" s="22">
+      <c r="C46" s="23">
         <v>44.354999999999997</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="23">
         <v>52.195</v>
       </c>
-      <c r="E46" s="23">
-        <v>1</v>
-      </c>
-      <c r="F46" s="22">
+      <c r="E46" s="24">
+        <v>1</v>
+      </c>
+      <c r="F46" s="23">
         <v>44.475999999999999</v>
       </c>
-      <c r="G46" s="22">
+      <c r="G46" s="23">
         <v>52.075000000000003</v>
       </c>
-      <c r="H46" s="23">
+      <c r="H46" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="22">
+      <c r="A47" s="23">
         <v>42.777999999999999</v>
       </c>
-      <c r="B47" s="22">
+      <c r="B47" s="23">
         <v>9.7850000000000001</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="23">
         <v>38.857999999999997</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="23">
         <v>46.698</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="24">
         <v>0</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="23">
         <v>38.738999999999997</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="23">
         <v>46.817</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="22">
+      <c r="A48" s="23">
         <v>46.618000000000002</v>
       </c>
-      <c r="B48" s="22">
+      <c r="B48" s="23">
         <v>10.548999999999999</v>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="23">
         <v>42.698</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="23">
         <v>50.537999999999997</v>
       </c>
-      <c r="E48" s="23">
-        <v>1</v>
-      </c>
-      <c r="F48" s="22">
+      <c r="E48" s="24">
+        <v>1</v>
+      </c>
+      <c r="F48" s="23">
         <v>42.264000000000003</v>
       </c>
-      <c r="G48" s="22">
+      <c r="G48" s="23">
         <v>50.972000000000001</v>
       </c>
-      <c r="H48" s="23">
+      <c r="H48" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="22">
+      <c r="A49" s="23">
         <v>49.11</v>
       </c>
-      <c r="B49" s="22">
+      <c r="B49" s="23">
         <v>11.172000000000001</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="23">
         <v>45.19</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="23">
         <v>53.03</v>
       </c>
-      <c r="E49" s="23">
-        <v>1</v>
-      </c>
-      <c r="F49" s="22">
+      <c r="E49" s="24">
+        <v>1</v>
+      </c>
+      <c r="F49" s="23">
         <v>44.499000000000002</v>
       </c>
-      <c r="G49" s="22">
+      <c r="G49" s="23">
         <v>53.722000000000001</v>
       </c>
-      <c r="H49" s="23">
+      <c r="H49" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="22">
+      <c r="A50" s="23">
         <v>45.954999999999998</v>
       </c>
-      <c r="B50" s="22">
+      <c r="B50" s="23">
         <v>9.4429999999999996</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="23">
         <v>42.034999999999997</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="23">
         <v>49.875</v>
       </c>
-      <c r="E50" s="23">
-        <v>1</v>
-      </c>
-      <c r="F50" s="22">
+      <c r="E50" s="24">
+        <v>1</v>
+      </c>
+      <c r="F50" s="23">
         <v>42.057000000000002</v>
       </c>
-      <c r="G50" s="22">
+      <c r="G50" s="23">
         <v>49.851999999999997</v>
       </c>
-      <c r="H50" s="23">
+      <c r="H50" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="22">
+      <c r="A51" s="23">
         <v>49.514000000000003</v>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="23">
         <v>11.587</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="23">
         <v>45.594000000000001</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="23">
         <v>53.433999999999997</v>
       </c>
-      <c r="E51" s="23">
-        <v>1</v>
-      </c>
-      <c r="F51" s="22">
+      <c r="E51" s="24">
+        <v>1</v>
+      </c>
+      <c r="F51" s="23">
         <v>44.731000000000002</v>
       </c>
-      <c r="G51" s="22">
+      <c r="G51" s="23">
         <v>54.296999999999997</v>
       </c>
-      <c r="H51" s="23">
+      <c r="H51" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="22">
+      <c r="A52" s="23">
         <v>45.094000000000001</v>
       </c>
-      <c r="B52" s="22">
+      <c r="B52" s="23">
         <v>11.191000000000001</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="23">
         <v>41.173999999999999</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="23">
         <v>49.014000000000003</v>
       </c>
-      <c r="E52" s="23">
-        <v>1</v>
-      </c>
-      <c r="F52" s="22">
+      <c r="E52" s="24">
+        <v>1</v>
+      </c>
+      <c r="F52" s="23">
         <v>40.473999999999997</v>
       </c>
-      <c r="G52" s="22">
+      <c r="G52" s="23">
         <v>49.713000000000001</v>
       </c>
-      <c r="H52" s="23">
+      <c r="H52" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="22">
+      <c r="A53" s="23">
         <v>43.392000000000003</v>
       </c>
-      <c r="B53" s="22">
+      <c r="B53" s="23">
         <v>10.513</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="23">
         <v>39.472000000000001</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="23">
         <v>47.311999999999998</v>
       </c>
-      <c r="E53" s="23">
-        <v>1</v>
-      </c>
-      <c r="F53" s="22">
+      <c r="E53" s="24">
+        <v>1</v>
+      </c>
+      <c r="F53" s="23">
         <v>39.052</v>
       </c>
-      <c r="G53" s="22">
+      <c r="G53" s="23">
         <v>47.731000000000002</v>
       </c>
-      <c r="H53" s="23">
+      <c r="H53" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="22">
+      <c r="A54" s="23">
         <v>49.338000000000001</v>
       </c>
-      <c r="B54" s="22">
+      <c r="B54" s="23">
         <v>11.343999999999999</v>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="23">
         <v>45.417999999999999</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="23">
         <v>53.258000000000003</v>
       </c>
-      <c r="E54" s="23">
-        <v>1</v>
-      </c>
-      <c r="F54" s="22">
+      <c r="E54" s="24">
+        <v>1</v>
+      </c>
+      <c r="F54" s="23">
         <v>44.655000000000001</v>
       </c>
-      <c r="G54" s="22">
+      <c r="G54" s="23">
         <v>54.021000000000001</v>
       </c>
-      <c r="H54" s="23">
+      <c r="H54" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="22">
+      <c r="A55" s="23">
         <v>44.686</v>
       </c>
-      <c r="B55" s="22">
+      <c r="B55" s="23">
         <v>9.1959999999999997</v>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="23">
         <v>40.765999999999998</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="23">
         <v>48.606000000000002</v>
       </c>
-      <c r="E55" s="23">
-        <v>1</v>
-      </c>
-      <c r="F55" s="22">
+      <c r="E55" s="24">
+        <v>1</v>
+      </c>
+      <c r="F55" s="23">
         <v>40.89</v>
       </c>
-      <c r="G55" s="22">
+      <c r="G55" s="23">
         <v>48.481999999999999</v>
       </c>
-      <c r="H55" s="23">
+      <c r="H55" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22">
+      <c r="A56" s="23">
         <v>46.701999999999998</v>
       </c>
-      <c r="B56" s="22">
+      <c r="B56" s="23">
         <v>11.601000000000001</v>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="23">
         <v>42.781999999999996</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="23">
         <v>50.622</v>
       </c>
-      <c r="E56" s="23">
-        <v>1</v>
-      </c>
-      <c r="F56" s="22">
+      <c r="E56" s="24">
+        <v>1</v>
+      </c>
+      <c r="F56" s="23">
         <v>41.912999999999997</v>
       </c>
-      <c r="G56" s="22">
+      <c r="G56" s="23">
         <v>51.49</v>
       </c>
-      <c r="H56" s="23">
+      <c r="H56" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="22">
+      <c r="A57" s="23">
         <v>47.116999999999997</v>
       </c>
-      <c r="B57" s="22">
+      <c r="B57" s="23">
         <v>8.1780000000000008</v>
       </c>
-      <c r="C57" s="22">
+      <c r="C57" s="23">
         <v>43.198</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="23">
         <v>51.036999999999999</v>
       </c>
-      <c r="E57" s="23">
-        <v>1</v>
-      </c>
-      <c r="F57" s="22">
+      <c r="E57" s="24">
+        <v>1</v>
+      </c>
+      <c r="F57" s="23">
         <v>43.741999999999997</v>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="23">
         <v>50.493000000000002</v>
       </c>
-      <c r="H57" s="23">
+      <c r="H57" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="22">
+      <c r="A58" s="23">
         <v>46.862000000000002</v>
       </c>
-      <c r="B58" s="22">
+      <c r="B58" s="23">
         <v>8.9860000000000007</v>
       </c>
-      <c r="C58" s="22">
+      <c r="C58" s="23">
         <v>42.942</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="23">
         <v>50.781999999999996</v>
       </c>
-      <c r="E58" s="23">
-        <v>1</v>
-      </c>
-      <c r="F58" s="22">
+      <c r="E58" s="24">
+        <v>1</v>
+      </c>
+      <c r="F58" s="23">
         <v>43.152999999999999</v>
       </c>
-      <c r="G58" s="22">
+      <c r="G58" s="23">
         <v>50.570999999999998</v>
       </c>
-      <c r="H58" s="23">
+      <c r="H58" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="22">
+      <c r="A59" s="23">
         <v>49.780999999999999</v>
       </c>
-      <c r="B59" s="22">
+      <c r="B59" s="23">
         <v>10.173999999999999</v>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="23">
         <v>45.860999999999997</v>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="23">
         <v>53.701000000000001</v>
       </c>
-      <c r="E59" s="23">
-        <v>1</v>
-      </c>
-      <c r="F59" s="22">
+      <c r="E59" s="24">
+        <v>1</v>
+      </c>
+      <c r="F59" s="23">
         <v>45.582000000000001</v>
       </c>
-      <c r="G59" s="22">
+      <c r="G59" s="23">
         <v>53.981000000000002</v>
       </c>
-      <c r="H59" s="23">
+      <c r="H59" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="22">
+      <c r="A60" s="23">
         <v>49.03</v>
       </c>
-      <c r="B60" s="22">
+      <c r="B60" s="23">
         <v>11.259</v>
       </c>
-      <c r="C60" s="22">
+      <c r="C60" s="23">
         <v>45.11</v>
       </c>
-      <c r="D60" s="22">
+      <c r="D60" s="23">
         <v>52.95</v>
       </c>
-      <c r="E60" s="23">
-        <v>1</v>
-      </c>
-      <c r="F60" s="22">
+      <c r="E60" s="24">
+        <v>1</v>
+      </c>
+      <c r="F60" s="23">
         <v>44.381999999999998</v>
       </c>
-      <c r="G60" s="22">
+      <c r="G60" s="23">
         <v>53.677999999999997</v>
       </c>
-      <c r="H60" s="23">
+      <c r="H60" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="22">
+      <c r="A61" s="23">
         <v>45.124000000000002</v>
       </c>
-      <c r="B61" s="22">
+      <c r="B61" s="23">
         <v>9.0020000000000007</v>
       </c>
-      <c r="C61" s="22">
+      <c r="C61" s="23">
         <v>41.204000000000001</v>
       </c>
-      <c r="D61" s="22">
+      <c r="D61" s="23">
         <v>49.043999999999997</v>
       </c>
-      <c r="E61" s="23">
-        <v>1</v>
-      </c>
-      <c r="F61" s="22">
+      <c r="E61" s="24">
+        <v>1</v>
+      </c>
+      <c r="F61" s="23">
         <v>41.408000000000001</v>
       </c>
-      <c r="G61" s="22">
+      <c r="G61" s="23">
         <v>48.838999999999999</v>
       </c>
-      <c r="H61" s="23">
+      <c r="H61" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="22">
+      <c r="A62" s="23">
         <v>46.326000000000001</v>
       </c>
-      <c r="B62" s="22">
+      <c r="B62" s="23">
         <v>10.5</v>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="23">
         <v>42.405999999999999</v>
       </c>
-      <c r="D62" s="22">
+      <c r="D62" s="23">
         <v>50.246000000000002</v>
       </c>
-      <c r="E62" s="23">
-        <v>1</v>
-      </c>
-      <c r="F62" s="22">
+      <c r="E62" s="24">
+        <v>1</v>
+      </c>
+      <c r="F62" s="23">
         <v>41.991999999999997</v>
       </c>
-      <c r="G62" s="22">
+      <c r="G62" s="23">
         <v>50.66</v>
       </c>
-      <c r="H62" s="23">
+      <c r="H62" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="22">
+      <c r="A63" s="23">
         <v>47.454000000000001</v>
       </c>
-      <c r="B63" s="22">
+      <c r="B63" s="23">
         <v>7.2919999999999998</v>
       </c>
-      <c r="C63" s="22">
+      <c r="C63" s="23">
         <v>43.533999999999999</v>
       </c>
-      <c r="D63" s="22">
+      <c r="D63" s="23">
         <v>51.374000000000002</v>
       </c>
-      <c r="E63" s="23">
-        <v>1</v>
-      </c>
-      <c r="F63" s="22">
+      <c r="E63" s="24">
+        <v>1</v>
+      </c>
+      <c r="F63" s="23">
         <v>44.444000000000003</v>
       </c>
-      <c r="G63" s="22">
+      <c r="G63" s="23">
         <v>50.463999999999999</v>
       </c>
-      <c r="H63" s="23">
+      <c r="H63" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="22">
+      <c r="A64" s="23">
         <v>46.588000000000001</v>
       </c>
-      <c r="B64" s="22">
+      <c r="B64" s="23">
         <v>8.5579999999999998</v>
       </c>
-      <c r="C64" s="22">
+      <c r="C64" s="23">
         <v>42.667999999999999</v>
       </c>
-      <c r="D64" s="22">
+      <c r="D64" s="23">
         <v>50.508000000000003</v>
       </c>
-      <c r="E64" s="23">
-        <v>1</v>
-      </c>
-      <c r="F64" s="22">
+      <c r="E64" s="24">
+        <v>1</v>
+      </c>
+      <c r="F64" s="23">
         <v>43.055999999999997</v>
       </c>
-      <c r="G64" s="22">
+      <c r="G64" s="23">
         <v>50.121000000000002</v>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="22">
+      <c r="A65" s="23">
         <v>44.643000000000001</v>
       </c>
-      <c r="B65" s="22">
+      <c r="B65" s="23">
         <v>9.8170000000000002</v>
       </c>
-      <c r="C65" s="22">
+      <c r="C65" s="23">
         <v>40.722999999999999</v>
       </c>
-      <c r="D65" s="22">
+      <c r="D65" s="23">
         <v>48.563000000000002</v>
       </c>
-      <c r="E65" s="23">
-        <v>1</v>
-      </c>
-      <c r="F65" s="22">
+      <c r="E65" s="24">
+        <v>1</v>
+      </c>
+      <c r="F65" s="23">
         <v>40.591000000000001</v>
       </c>
-      <c r="G65" s="22">
+      <c r="G65" s="23">
         <v>48.695</v>
       </c>
-      <c r="H65" s="23">
+      <c r="H65" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="22">
+      <c r="A66" s="23">
         <v>47.640999999999998</v>
       </c>
-      <c r="B66" s="22">
+      <c r="B66" s="23">
         <v>9.4689999999999994</v>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="23">
         <v>43.720999999999997</v>
       </c>
-      <c r="D66" s="22">
+      <c r="D66" s="23">
         <v>51.561</v>
       </c>
-      <c r="E66" s="23">
-        <v>1</v>
-      </c>
-      <c r="F66" s="22">
+      <c r="E66" s="24">
+        <v>1</v>
+      </c>
+      <c r="F66" s="23">
         <v>43.731999999999999</v>
       </c>
-      <c r="G66" s="22">
+      <c r="G66" s="23">
         <v>51.548999999999999</v>
       </c>
-      <c r="H66" s="23">
+      <c r="H66" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="22">
+      <c r="A67" s="23">
         <v>47.969000000000001</v>
       </c>
-      <c r="B67" s="22">
+      <c r="B67" s="23">
         <v>9.1579999999999995</v>
       </c>
-      <c r="C67" s="22">
+      <c r="C67" s="23">
         <v>44.048999999999999</v>
       </c>
-      <c r="D67" s="22">
+      <c r="D67" s="23">
         <v>51.889000000000003</v>
       </c>
-      <c r="E67" s="23">
-        <v>1</v>
-      </c>
-      <c r="F67" s="22">
+      <c r="E67" s="24">
+        <v>1</v>
+      </c>
+      <c r="F67" s="23">
         <v>44.189</v>
       </c>
-      <c r="G67" s="22">
+      <c r="G67" s="23">
         <v>51.749000000000002</v>
       </c>
-      <c r="H67" s="23">
+      <c r="H67" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="22">
+      <c r="A68" s="23">
         <v>47.911000000000001</v>
       </c>
-      <c r="B68" s="22">
+      <c r="B68" s="23">
         <v>8.8040000000000003</v>
       </c>
-      <c r="C68" s="22">
+      <c r="C68" s="23">
         <v>43.991</v>
       </c>
-      <c r="D68" s="22">
+      <c r="D68" s="23">
         <v>51.831000000000003</v>
       </c>
-      <c r="E68" s="23">
-        <v>1</v>
-      </c>
-      <c r="F68" s="22">
+      <c r="E68" s="24">
+        <v>1</v>
+      </c>
+      <c r="F68" s="23">
         <v>44.276000000000003</v>
       </c>
-      <c r="G68" s="22">
+      <c r="G68" s="23">
         <v>51.545000000000002</v>
       </c>
-      <c r="H68" s="23">
+      <c r="H68" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="22">
+      <c r="A69" s="23">
         <v>46.131</v>
       </c>
-      <c r="B69" s="22">
+      <c r="B69" s="23">
         <v>12.099</v>
       </c>
-      <c r="C69" s="22">
+      <c r="C69" s="23">
         <v>42.210999999999999</v>
       </c>
-      <c r="D69" s="22">
+      <c r="D69" s="23">
         <v>50.051000000000002</v>
       </c>
-      <c r="E69" s="23">
-        <v>1</v>
-      </c>
-      <c r="F69" s="22">
+      <c r="E69" s="24">
+        <v>1</v>
+      </c>
+      <c r="F69" s="23">
         <v>41.137</v>
       </c>
-      <c r="G69" s="22">
+      <c r="G69" s="23">
         <v>51.125</v>
       </c>
-      <c r="H69" s="23">
+      <c r="H69" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="22">
+      <c r="A70" s="23">
         <v>45.573</v>
       </c>
-      <c r="B70" s="22">
+      <c r="B70" s="23">
         <v>12.728</v>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="23">
         <v>41.654000000000003</v>
       </c>
-      <c r="D70" s="22">
+      <c r="D70" s="23">
         <v>49.493000000000002</v>
       </c>
-      <c r="E70" s="23">
-        <v>1</v>
-      </c>
-      <c r="F70" s="22">
+      <c r="E70" s="24">
+        <v>1</v>
+      </c>
+      <c r="F70" s="23">
         <v>40.32</v>
       </c>
-      <c r="G70" s="22">
+      <c r="G70" s="23">
         <v>50.826999999999998</v>
       </c>
-      <c r="H70" s="23">
+      <c r="H70" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="22">
+      <c r="A71" s="23">
         <v>45.593000000000004</v>
       </c>
-      <c r="B71" s="22">
+      <c r="B71" s="23">
         <v>9.4879999999999995</v>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="23">
         <v>41.673000000000002</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="23">
         <v>49.512999999999998</v>
       </c>
-      <c r="E71" s="23">
-        <v>1</v>
-      </c>
-      <c r="F71" s="22">
+      <c r="E71" s="24">
+        <v>1</v>
+      </c>
+      <c r="F71" s="23">
         <v>41.677</v>
       </c>
-      <c r="G71" s="22">
+      <c r="G71" s="23">
         <v>49.509</v>
       </c>
-      <c r="H71" s="23">
+      <c r="H71" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="22">
+      <c r="A72" s="23">
         <v>46.265999999999998</v>
       </c>
-      <c r="B72" s="22">
+      <c r="B72" s="23">
         <v>9.1839999999999993</v>
       </c>
-      <c r="C72" s="22">
+      <c r="C72" s="23">
         <v>42.345999999999997</v>
       </c>
-      <c r="D72" s="22">
+      <c r="D72" s="23">
         <v>50.186</v>
       </c>
-      <c r="E72" s="23">
-        <v>1</v>
-      </c>
-      <c r="F72" s="22">
+      <c r="E72" s="24">
+        <v>1</v>
+      </c>
+      <c r="F72" s="23">
         <v>42.475000000000001</v>
       </c>
-      <c r="G72" s="22">
+      <c r="G72" s="23">
         <v>50.057000000000002</v>
       </c>
-      <c r="H72" s="23">
+      <c r="H72" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="22">
+      <c r="A73" s="23">
         <v>46.097999999999999</v>
       </c>
-      <c r="B73" s="22">
+      <c r="B73" s="23">
         <v>8.4649999999999999</v>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="23">
         <v>42.177999999999997</v>
       </c>
-      <c r="D73" s="22">
+      <c r="D73" s="23">
         <v>50.018000000000001</v>
       </c>
-      <c r="E73" s="23">
-        <v>1</v>
-      </c>
-      <c r="F73" s="22">
+      <c r="E73" s="24">
+        <v>1</v>
+      </c>
+      <c r="F73" s="23">
         <v>42.603999999999999</v>
       </c>
-      <c r="G73" s="22">
+      <c r="G73" s="23">
         <v>49.593000000000004</v>
       </c>
-      <c r="H73" s="23">
+      <c r="H73" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="22">
+      <c r="A74" s="23">
         <v>47.094000000000001</v>
       </c>
-      <c r="B74" s="22">
+      <c r="B74" s="23">
         <v>8.6259999999999994</v>
       </c>
-      <c r="C74" s="22">
+      <c r="C74" s="23">
         <v>43.173999999999999</v>
       </c>
-      <c r="D74" s="22">
+      <c r="D74" s="23">
         <v>51.014000000000003</v>
       </c>
-      <c r="E74" s="23">
-        <v>1</v>
-      </c>
-      <c r="F74" s="22">
+      <c r="E74" s="24">
+        <v>1</v>
+      </c>
+      <c r="F74" s="23">
         <v>43.533999999999999</v>
       </c>
-      <c r="G74" s="22">
+      <c r="G74" s="23">
         <v>50.655000000000001</v>
       </c>
-      <c r="H74" s="23">
+      <c r="H74" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="22">
+      <c r="A75" s="23">
         <v>41.555</v>
       </c>
-      <c r="B75" s="22">
+      <c r="B75" s="23">
         <v>11.946999999999999</v>
       </c>
-      <c r="C75" s="22">
+      <c r="C75" s="23">
         <v>37.634999999999998</v>
       </c>
-      <c r="D75" s="22">
+      <c r="D75" s="23">
         <v>45.475000000000001</v>
       </c>
-      <c r="E75" s="23">
+      <c r="E75" s="24">
         <v>0</v>
       </c>
-      <c r="F75" s="22">
+      <c r="F75" s="23">
         <v>36.624000000000002</v>
       </c>
-      <c r="G75" s="22">
+      <c r="G75" s="23">
         <v>46.487000000000002</v>
       </c>
-      <c r="H75" s="23">
+      <c r="H75" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="22">
+      <c r="A76" s="23">
         <v>45.962000000000003</v>
       </c>
-      <c r="B76" s="22">
+      <c r="B76" s="23">
         <v>8.3089999999999993</v>
       </c>
-      <c r="C76" s="22">
+      <c r="C76" s="23">
         <v>42.042000000000002</v>
       </c>
-      <c r="D76" s="22">
+      <c r="D76" s="23">
         <v>49.881999999999998</v>
       </c>
-      <c r="E76" s="23">
-        <v>1</v>
-      </c>
-      <c r="F76" s="22">
+      <c r="E76" s="24">
+        <v>1</v>
+      </c>
+      <c r="F76" s="23">
         <v>42.531999999999996</v>
       </c>
-      <c r="G76" s="22">
+      <c r="G76" s="23">
         <v>49.390999999999998</v>
       </c>
-      <c r="H76" s="23">
+      <c r="H76" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="22">
+      <c r="A77" s="23">
         <v>45.767000000000003</v>
       </c>
-      <c r="B77" s="22">
+      <c r="B77" s="23">
         <v>12.423</v>
       </c>
-      <c r="C77" s="22">
+      <c r="C77" s="23">
         <v>41.847000000000001</v>
       </c>
-      <c r="D77" s="22">
+      <c r="D77" s="23">
         <v>49.686999999999998</v>
       </c>
-      <c r="E77" s="23">
-        <v>1</v>
-      </c>
-      <c r="F77" s="22">
+      <c r="E77" s="24">
+        <v>1</v>
+      </c>
+      <c r="F77" s="23">
         <v>40.639000000000003</v>
       </c>
-      <c r="G77" s="22">
+      <c r="G77" s="23">
         <v>50.895000000000003</v>
       </c>
-      <c r="H77" s="23">
+      <c r="H77" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="22">
+      <c r="A78" s="23">
         <v>44.05</v>
       </c>
-      <c r="B78" s="22">
+      <c r="B78" s="23">
         <v>9.3849999999999998</v>
       </c>
-      <c r="C78" s="22">
+      <c r="C78" s="23">
         <v>40.130000000000003</v>
       </c>
-      <c r="D78" s="22">
+      <c r="D78" s="23">
         <v>47.97</v>
       </c>
-      <c r="E78" s="23">
-        <v>1</v>
-      </c>
-      <c r="F78" s="22">
+      <c r="E78" s="24">
+        <v>1</v>
+      </c>
+      <c r="F78" s="23">
         <v>40.176000000000002</v>
       </c>
-      <c r="G78" s="22">
+      <c r="G78" s="23">
         <v>47.923999999999999</v>
       </c>
-      <c r="H78" s="23">
+      <c r="H78" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="22">
+      <c r="A79" s="23">
         <v>46.186999999999998</v>
       </c>
-      <c r="B79" s="22">
+      <c r="B79" s="23">
         <v>11.891999999999999</v>
       </c>
-      <c r="C79" s="22">
+      <c r="C79" s="23">
         <v>42.267000000000003</v>
       </c>
-      <c r="D79" s="22">
+      <c r="D79" s="23">
         <v>50.106000000000002</v>
       </c>
-      <c r="E79" s="23">
-        <v>1</v>
-      </c>
-      <c r="F79" s="22">
+      <c r="E79" s="24">
+        <v>1</v>
+      </c>
+      <c r="F79" s="23">
         <v>41.277999999999999</v>
       </c>
-      <c r="G79" s="22">
+      <c r="G79" s="23">
         <v>51.094999999999999</v>
       </c>
-      <c r="H79" s="23">
+      <c r="H79" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="22">
+      <c r="A80" s="23">
         <v>49.027000000000001</v>
       </c>
-      <c r="B80" s="22">
+      <c r="B80" s="23">
         <v>10.33</v>
       </c>
-      <c r="C80" s="22">
+      <c r="C80" s="23">
         <v>45.106999999999999</v>
       </c>
-      <c r="D80" s="22">
+      <c r="D80" s="23">
         <v>52.947000000000003</v>
       </c>
-      <c r="E80" s="23">
-        <v>1</v>
-      </c>
-      <c r="F80" s="22">
+      <c r="E80" s="24">
+        <v>1</v>
+      </c>
+      <c r="F80" s="23">
         <v>44.762999999999998</v>
       </c>
-      <c r="G80" s="22">
+      <c r="G80" s="23">
         <v>53.290999999999997</v>
       </c>
-      <c r="H80" s="23">
+      <c r="H80" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="22">
+      <c r="A81" s="23">
         <v>47.564</v>
       </c>
-      <c r="B81" s="22">
+      <c r="B81" s="23">
         <v>8.6969999999999992</v>
       </c>
-      <c r="C81" s="22">
+      <c r="C81" s="23">
         <v>43.643999999999998</v>
       </c>
-      <c r="D81" s="22">
+      <c r="D81" s="23">
         <v>51.484000000000002</v>
       </c>
-      <c r="E81" s="23">
-        <v>1</v>
-      </c>
-      <c r="F81" s="22">
+      <c r="E81" s="24">
+        <v>1</v>
+      </c>
+      <c r="F81" s="23">
         <v>43.973999999999997</v>
       </c>
-      <c r="G81" s="22">
+      <c r="G81" s="23">
         <v>51.154000000000003</v>
       </c>
-      <c r="H81" s="23">
+      <c r="H81" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="22">
+      <c r="A82" s="23">
         <v>47.042000000000002</v>
       </c>
-      <c r="B82" s="22">
+      <c r="B82" s="23">
         <v>8.5709999999999997</v>
       </c>
-      <c r="C82" s="22">
+      <c r="C82" s="23">
         <v>43.122</v>
       </c>
-      <c r="D82" s="22">
+      <c r="D82" s="23">
         <v>50.962000000000003</v>
       </c>
-      <c r="E82" s="23">
-        <v>1</v>
-      </c>
-      <c r="F82" s="22">
+      <c r="E82" s="24">
+        <v>1</v>
+      </c>
+      <c r="F82" s="23">
         <v>43.503999999999998</v>
       </c>
-      <c r="G82" s="22">
+      <c r="G82" s="23">
         <v>50.58</v>
       </c>
-      <c r="H82" s="23">
+      <c r="H82" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="22">
+      <c r="A83" s="23">
         <v>46.377000000000002</v>
       </c>
-      <c r="B83" s="22">
+      <c r="B83" s="23">
         <v>9.9809999999999999</v>
       </c>
-      <c r="C83" s="22">
+      <c r="C83" s="23">
         <v>42.457000000000001</v>
       </c>
-      <c r="D83" s="22">
+      <c r="D83" s="23">
         <v>50.295999999999999</v>
       </c>
-      <c r="E83" s="23">
-        <v>1</v>
-      </c>
-      <c r="F83" s="22">
+      <c r="E83" s="24">
+        <v>1</v>
+      </c>
+      <c r="F83" s="23">
         <v>42.256999999999998</v>
       </c>
-      <c r="G83" s="22">
+      <c r="G83" s="23">
         <v>50.496000000000002</v>
       </c>
-      <c r="H83" s="23">
+      <c r="H83" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="22">
+      <c r="A84" s="23">
         <v>47.323999999999998</v>
       </c>
-      <c r="B84" s="22">
+      <c r="B84" s="23">
         <v>10.551</v>
       </c>
-      <c r="C84" s="22">
+      <c r="C84" s="23">
         <v>43.404000000000003</v>
       </c>
-      <c r="D84" s="22">
+      <c r="D84" s="23">
         <v>51.244</v>
       </c>
-      <c r="E84" s="23">
-        <v>1</v>
-      </c>
-      <c r="F84" s="22">
+      <c r="E84" s="24">
+        <v>1</v>
+      </c>
+      <c r="F84" s="23">
         <v>42.969000000000001</v>
       </c>
-      <c r="G84" s="22">
+      <c r="G84" s="23">
         <v>51.679000000000002</v>
       </c>
-      <c r="H84" s="23">
+      <c r="H84" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="22">
+      <c r="A85" s="23">
         <v>44.825000000000003</v>
       </c>
-      <c r="B85" s="22">
+      <c r="B85" s="23">
         <v>8.3030000000000008</v>
       </c>
-      <c r="C85" s="22">
+      <c r="C85" s="23">
         <v>40.905000000000001</v>
       </c>
-      <c r="D85" s="22">
+      <c r="D85" s="23">
         <v>48.744999999999997</v>
       </c>
-      <c r="E85" s="23">
-        <v>1</v>
-      </c>
-      <c r="F85" s="22">
+      <c r="E85" s="24">
+        <v>1</v>
+      </c>
+      <c r="F85" s="23">
         <v>41.398000000000003</v>
       </c>
-      <c r="G85" s="22">
+      <c r="G85" s="23">
         <v>48.252000000000002</v>
       </c>
-      <c r="H85" s="23">
+      <c r="H85" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="22">
+      <c r="A86" s="23">
         <v>48.04</v>
       </c>
-      <c r="B86" s="22">
+      <c r="B86" s="23">
         <v>8.4580000000000002</v>
       </c>
-      <c r="C86" s="22">
+      <c r="C86" s="23">
         <v>44.12</v>
       </c>
-      <c r="D86" s="22">
+      <c r="D86" s="23">
         <v>51.96</v>
       </c>
-      <c r="E86" s="23">
-        <v>1</v>
-      </c>
-      <c r="F86" s="22">
+      <c r="E86" s="24">
+        <v>1</v>
+      </c>
+      <c r="F86" s="23">
         <v>44.548999999999999</v>
       </c>
-      <c r="G86" s="22">
+      <c r="G86" s="23">
         <v>51.530999999999999</v>
       </c>
-      <c r="H86" s="23">
+      <c r="H86" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="22">
+      <c r="A87" s="23">
         <v>47.393000000000001</v>
       </c>
-      <c r="B87" s="22">
+      <c r="B87" s="23">
         <v>8.9149999999999991</v>
       </c>
-      <c r="C87" s="22">
+      <c r="C87" s="23">
         <v>43.472999999999999</v>
       </c>
-      <c r="D87" s="22">
+      <c r="D87" s="23">
         <v>51.313000000000002</v>
       </c>
-      <c r="E87" s="23">
-        <v>1</v>
-      </c>
-      <c r="F87" s="22">
+      <c r="E87" s="24">
+        <v>1</v>
+      </c>
+      <c r="F87" s="23">
         <v>43.713999999999999</v>
       </c>
-      <c r="G87" s="22">
+      <c r="G87" s="23">
         <v>51.073</v>
       </c>
-      <c r="H87" s="23">
+      <c r="H87" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="22">
+      <c r="A88" s="23">
         <v>45.924999999999997</v>
       </c>
-      <c r="B88" s="22">
+      <c r="B88" s="23">
         <v>9.2349999999999994</v>
       </c>
-      <c r="C88" s="22">
+      <c r="C88" s="23">
         <v>42.005000000000003</v>
       </c>
-      <c r="D88" s="22">
+      <c r="D88" s="23">
         <v>49.844999999999999</v>
       </c>
-      <c r="E88" s="23">
-        <v>1</v>
-      </c>
-      <c r="F88" s="22">
+      <c r="E88" s="24">
+        <v>1</v>
+      </c>
+      <c r="F88" s="23">
         <v>42.113</v>
       </c>
-      <c r="G88" s="22">
+      <c r="G88" s="23">
         <v>49.737000000000002</v>
       </c>
-      <c r="H88" s="23">
+      <c r="H88" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="22">
+      <c r="A89" s="23">
         <v>45.265000000000001</v>
       </c>
-      <c r="B89" s="22">
+      <c r="B89" s="23">
         <v>9.7550000000000008</v>
       </c>
-      <c r="C89" s="22">
+      <c r="C89" s="23">
         <v>41.344999999999999</v>
       </c>
-      <c r="D89" s="22">
+      <c r="D89" s="23">
         <v>49.185000000000002</v>
       </c>
-      <c r="E89" s="23">
-        <v>1</v>
-      </c>
-      <c r="F89" s="22">
+      <c r="E89" s="24">
+        <v>1</v>
+      </c>
+      <c r="F89" s="23">
         <v>41.238</v>
       </c>
-      <c r="G89" s="22">
+      <c r="G89" s="23">
         <v>49.290999999999997</v>
       </c>
-      <c r="H89" s="23">
+      <c r="H89" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="22">
+      <c r="A90" s="23">
         <v>48.213999999999999</v>
       </c>
-      <c r="B90" s="22">
+      <c r="B90" s="23">
         <v>10.657999999999999</v>
       </c>
-      <c r="C90" s="22">
+      <c r="C90" s="23">
         <v>44.293999999999997</v>
       </c>
-      <c r="D90" s="22">
+      <c r="D90" s="23">
         <v>52.134</v>
       </c>
-      <c r="E90" s="23">
-        <v>1</v>
-      </c>
-      <c r="F90" s="22">
+      <c r="E90" s="24">
+        <v>1</v>
+      </c>
+      <c r="F90" s="23">
         <v>43.814999999999998</v>
       </c>
-      <c r="G90" s="22">
+      <c r="G90" s="23">
         <v>52.613</v>
       </c>
-      <c r="H90" s="23">
+      <c r="H90" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="22">
+      <c r="A91" s="23">
         <v>46.228000000000002</v>
       </c>
-      <c r="B91" s="22">
+      <c r="B91" s="23">
         <v>11.183999999999999</v>
       </c>
-      <c r="C91" s="22">
+      <c r="C91" s="23">
         <v>42.308</v>
       </c>
-      <c r="D91" s="22">
+      <c r="D91" s="23">
         <v>50.148000000000003</v>
       </c>
-      <c r="E91" s="23">
-        <v>1</v>
-      </c>
-      <c r="F91" s="22">
+      <c r="E91" s="24">
+        <v>1</v>
+      </c>
+      <c r="F91" s="23">
         <v>41.612000000000002</v>
       </c>
-      <c r="G91" s="22">
+      <c r="G91" s="23">
         <v>50.844000000000001</v>
       </c>
-      <c r="H91" s="23">
+      <c r="H91" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="22">
+      <c r="A92" s="23">
         <v>47.128999999999998</v>
       </c>
-      <c r="B92" s="22">
+      <c r="B92" s="23">
         <v>11.661</v>
       </c>
-      <c r="C92" s="22">
+      <c r="C92" s="23">
         <v>43.209000000000003</v>
       </c>
-      <c r="D92" s="22">
+      <c r="D92" s="23">
         <v>51.048999999999999</v>
       </c>
-      <c r="E92" s="23">
-        <v>1</v>
-      </c>
-      <c r="F92" s="22">
+      <c r="E92" s="24">
+        <v>1</v>
+      </c>
+      <c r="F92" s="23">
         <v>42.316000000000003</v>
       </c>
-      <c r="G92" s="22">
+      <c r="G92" s="23">
         <v>51.942999999999998</v>
       </c>
-      <c r="H92" s="23">
+      <c r="H92" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="22">
+      <c r="A93" s="23">
         <v>45.956000000000003</v>
       </c>
-      <c r="B93" s="22">
+      <c r="B93" s="23">
         <v>7.3460000000000001</v>
       </c>
-      <c r="C93" s="22">
+      <c r="C93" s="23">
         <v>42.036999999999999</v>
       </c>
-      <c r="D93" s="22">
+      <c r="D93" s="23">
         <v>49.875999999999998</v>
       </c>
-      <c r="E93" s="23">
-        <v>1</v>
-      </c>
-      <c r="F93" s="22">
+      <c r="E93" s="24">
+        <v>1</v>
+      </c>
+      <c r="F93" s="23">
         <v>42.923999999999999</v>
       </c>
-      <c r="G93" s="22">
+      <c r="G93" s="23">
         <v>48.988999999999997</v>
       </c>
-      <c r="H93" s="23">
+      <c r="H93" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="22">
+      <c r="A94" s="23">
         <v>48.415999999999997</v>
       </c>
-      <c r="B94" s="22">
+      <c r="B94" s="23">
         <v>10.394</v>
       </c>
-      <c r="C94" s="22">
+      <c r="C94" s="23">
         <v>44.496000000000002</v>
       </c>
-      <c r="D94" s="22">
+      <c r="D94" s="23">
         <v>52.335000000000001</v>
       </c>
-      <c r="E94" s="23">
-        <v>1</v>
-      </c>
-      <c r="F94" s="22">
+      <c r="E94" s="24">
+        <v>1</v>
+      </c>
+      <c r="F94" s="23">
         <v>44.125</v>
       </c>
-      <c r="G94" s="22">
+      <c r="G94" s="23">
         <v>52.706000000000003</v>
       </c>
-      <c r="H94" s="23">
+      <c r="H94" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="22">
+      <c r="A95" s="23">
         <v>45.728999999999999</v>
       </c>
-      <c r="B95" s="22">
+      <c r="B95" s="23">
         <v>9.6229999999999993</v>
       </c>
-      <c r="C95" s="22">
+      <c r="C95" s="23">
         <v>41.808999999999997</v>
       </c>
-      <c r="D95" s="22">
+      <c r="D95" s="23">
         <v>49.649000000000001</v>
       </c>
-      <c r="E95" s="23">
-        <v>1</v>
-      </c>
-      <c r="F95" s="22">
+      <c r="E95" s="24">
+        <v>1</v>
+      </c>
+      <c r="F95" s="23">
         <v>41.756999999999998</v>
       </c>
-      <c r="G95" s="22">
+      <c r="G95" s="23">
         <v>49.701000000000001</v>
       </c>
-      <c r="H95" s="23">
+      <c r="H95" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="22">
+      <c r="A96" s="23">
         <v>46.258000000000003</v>
       </c>
-      <c r="B96" s="22">
+      <c r="B96" s="23">
         <v>8.1880000000000006</v>
       </c>
-      <c r="C96" s="22">
+      <c r="C96" s="23">
         <v>42.338000000000001</v>
       </c>
-      <c r="D96" s="22">
+      <c r="D96" s="23">
         <v>50.177999999999997</v>
       </c>
-      <c r="E96" s="23">
-        <v>1</v>
-      </c>
-      <c r="F96" s="22">
+      <c r="E96" s="24">
+        <v>1</v>
+      </c>
+      <c r="F96" s="23">
         <v>42.878</v>
       </c>
-      <c r="G96" s="22">
+      <c r="G96" s="23">
         <v>49.637</v>
       </c>
-      <c r="H96" s="23">
+      <c r="H96" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="22">
+      <c r="A97" s="23">
         <v>47.731000000000002</v>
       </c>
-      <c r="B97" s="22">
+      <c r="B97" s="23">
         <v>10.079000000000001</v>
       </c>
-      <c r="C97" s="22">
+      <c r="C97" s="23">
         <v>43.811</v>
       </c>
-      <c r="D97" s="22">
+      <c r="D97" s="23">
         <v>51.651000000000003</v>
       </c>
-      <c r="E97" s="23">
-        <v>1</v>
-      </c>
-      <c r="F97" s="22">
+      <c r="E97" s="24">
+        <v>1</v>
+      </c>
+      <c r="F97" s="23">
         <v>43.57</v>
       </c>
-      <c r="G97" s="22">
+      <c r="G97" s="23">
         <v>51.892000000000003</v>
       </c>
-      <c r="H97" s="23">
+      <c r="H97" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="22">
+      <c r="A98" s="23">
         <v>43.140999999999998</v>
       </c>
-      <c r="B98" s="22">
+      <c r="B98" s="23">
         <v>10.478999999999999</v>
       </c>
-      <c r="C98" s="22">
+      <c r="C98" s="23">
         <v>39.220999999999997</v>
       </c>
-      <c r="D98" s="22">
+      <c r="D98" s="23">
         <v>47.061</v>
       </c>
-      <c r="E98" s="23">
-        <v>1</v>
-      </c>
-      <c r="F98" s="22">
+      <c r="E98" s="24">
+        <v>1</v>
+      </c>
+      <c r="F98" s="23">
         <v>38.816000000000003</v>
       </c>
-      <c r="G98" s="22">
+      <c r="G98" s="23">
         <v>47.466000000000001</v>
       </c>
-      <c r="H98" s="23">
+      <c r="H98" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="22">
+      <c r="A99" s="23">
         <v>46.982999999999997</v>
       </c>
-      <c r="B99" s="22">
+      <c r="B99" s="23">
         <v>9.3889999999999993</v>
       </c>
-      <c r="C99" s="22">
+      <c r="C99" s="23">
         <v>43.063000000000002</v>
       </c>
-      <c r="D99" s="22">
+      <c r="D99" s="23">
         <v>50.902000000000001</v>
       </c>
-      <c r="E99" s="23">
-        <v>1</v>
-      </c>
-      <c r="F99" s="22">
+      <c r="E99" s="24">
+        <v>1</v>
+      </c>
+      <c r="F99" s="23">
         <v>43.106999999999999</v>
       </c>
-      <c r="G99" s="22">
+      <c r="G99" s="23">
         <v>50.857999999999997</v>
       </c>
-      <c r="H99" s="23">
+      <c r="H99" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="22">
+      <c r="A100" s="23">
         <v>42.030999999999999</v>
       </c>
-      <c r="B100" s="22">
+      <c r="B100" s="23">
         <v>9.5660000000000007</v>
       </c>
-      <c r="C100" s="22">
+      <c r="C100" s="23">
         <v>38.110999999999997</v>
       </c>
-      <c r="D100" s="22">
+      <c r="D100" s="23">
         <v>45.951000000000001</v>
       </c>
-      <c r="E100" s="23">
+      <c r="E100" s="24">
         <v>0</v>
       </c>
-      <c r="F100" s="22">
+      <c r="F100" s="23">
         <v>38.082000000000001</v>
       </c>
-      <c r="G100" s="22">
+      <c r="G100" s="23">
         <v>45.98</v>
       </c>
-      <c r="H100" s="23">
+      <c r="H100" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="22">
+      <c r="A101" s="23">
         <v>45.466999999999999</v>
       </c>
-      <c r="B101" s="22">
+      <c r="B101" s="23">
         <v>9.4120000000000008</v>
       </c>
-      <c r="C101" s="22">
+      <c r="C101" s="23">
         <v>41.546999999999997</v>
       </c>
-      <c r="D101" s="22">
+      <c r="D101" s="23">
         <v>49.387</v>
       </c>
-      <c r="E101" s="23">
-        <v>1</v>
-      </c>
-      <c r="F101" s="22">
+      <c r="E101" s="24">
+        <v>1</v>
+      </c>
+      <c r="F101" s="23">
         <v>41.582000000000001</v>
       </c>
-      <c r="G101" s="22">
+      <c r="G101" s="23">
         <v>49.351999999999997</v>
       </c>
-      <c r="H101" s="23">
+      <c r="H101" s="24">
         <v>1</v>
       </c>
     </row>
